--- a/研发费用分摊表/2026年研发工时分配表（研发部填报）.xlsx
+++ b/研发费用分摊表/2026年研发工时分配表（研发部填报）.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="115">
   <si>
     <r>
       <rPr>
@@ -209,6 +209,33 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">一人（一台设备）当月分摊到各项目的工时合计不得大于当月总工时，【校验】列出现提示时必须修正后再提交。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">   校验提示含义：缺月份＝年度台账月份列没填（财务汇总时这行会被漏掉）；缺总工时＝当月总工时为 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；工时超出＝各项目工时合计大于当月总工时。</t>
     </r>
   </si>
   <si>
@@ -1457,7 +1484,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="B2:H29"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -1570,37 +1597,37 @@
       <c r="H11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="2" t="s">
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-    </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="3" t="s">
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="3" t="s">
@@ -1613,9 +1640,20 @@
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
     </row>
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+    </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -1626,25 +1664,25 @@
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1652,22 +1690,22 @@
         <v>1</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1675,19 +1713,19 @@
         <v>2</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H21" s="8"/>
     </row>
@@ -1696,19 +1734,19 @@
         <v>3</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H22" s="8"/>
     </row>
@@ -1717,19 +1755,19 @@
         <v>4</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H23" s="8"/>
     </row>
@@ -1738,19 +1776,19 @@
         <v>5</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H24" s="8"/>
     </row>
@@ -1759,7 +1797,7 @@
         <v>6</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="7"/>
@@ -1772,7 +1810,7 @@
         <v>7</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="7"/>
@@ -1785,7 +1823,7 @@
         <v>8</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="7"/>
@@ -1795,11 +1833,11 @@
     </row>
     <row r="29" customFormat="false" ht="97" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="B5:H5"/>
@@ -1813,11 +1851,12 @@
     <mergeCell ref="B13:H13"/>
     <mergeCell ref="B14:H14"/>
     <mergeCell ref="B15:H15"/>
+    <mergeCell ref="B16:H16"/>
     <mergeCell ref="B18:H18"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -1843,7 +1882,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
@@ -1863,7 +1902,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="O3" s="12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P3" s="13" t="n">
         <v>46266</v>
@@ -1872,19 +1911,19 @@
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G4" s="15"/>
       <c r="H4" s="15"/>
@@ -1895,13 +1934,13 @@
       <c r="M4" s="15"/>
       <c r="N4" s="15"/>
       <c r="O4" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P4" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q4" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1942,10 +1981,10 @@
         <v>RD08</v>
       </c>
       <c r="N5" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O5" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P5" s="14"/>
       <c r="Q5" s="14"/>
@@ -1997,7 +2036,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" s="18" t="n">
         <v>172.5</v>
@@ -2029,11 +2068,11 @@
         <v>0.753623188405797</v>
       </c>
       <c r="P7" s="21" t="str">
-        <f aca="false">IF($C7="","",IF($N7&gt;$D7,"工时超出","√"))</f>
+        <f aca="false">IF($C7="","",IF($D7=0,"缺总工时",IF(ROUND($N7-$D7,2)&gt;0,"工时超出","√")))</f>
         <v>√</v>
       </c>
       <c r="Q7" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2041,7 +2080,7 @@
         <v>2</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8" s="18" t="n">
         <v>172.5</v>
@@ -2071,7 +2110,7 @@
         <v>0.63768115942029</v>
       </c>
       <c r="P8" s="21" t="str">
-        <f aca="false">IF($C8="","",IF($N8&gt;$D8,"工时超出","√"))</f>
+        <f aca="false">IF($C8="","",IF($D8=0,"缺总工时",IF(ROUND($N8-$D8,2)&gt;0,"工时超出","√")))</f>
         <v>√</v>
       </c>
       <c r="Q8" s="8"/>
@@ -2081,7 +2120,7 @@
         <v>3</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9" s="18" t="n">
         <v>172.5</v>
@@ -2113,7 +2152,7 @@
         <v>0.695652173913044</v>
       </c>
       <c r="P9" s="21" t="str">
-        <f aca="false">IF($C9="","",IF($N9&gt;$D9,"工时超出","√"))</f>
+        <f aca="false">IF($C9="","",IF($D9=0,"缺总工时",IF(ROUND($N9-$D9,2)&gt;0,"工时超出","√")))</f>
         <v>√</v>
       </c>
       <c r="Q9" s="8"/>
@@ -2123,7 +2162,7 @@
         <v>4</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D10" s="18" t="n">
         <v>172.5</v>
@@ -2153,7 +2192,7 @@
         <v>0.695652173913044</v>
       </c>
       <c r="P10" s="21" t="str">
-        <f aca="false">IF($C10="","",IF($N10&gt;$D10,"工时超出","√"))</f>
+        <f aca="false">IF($C10="","",IF($D10=0,"缺总工时",IF(ROUND($N10-$D10,2)&gt;0,"工时超出","√")))</f>
         <v>√</v>
       </c>
       <c r="Q10" s="8"/>
@@ -2163,7 +2202,7 @@
         <v>5</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D11" s="18" t="n">
         <v>172.5</v>
@@ -2195,7 +2234,7 @@
         <v>0.811594202898551</v>
       </c>
       <c r="P11" s="21" t="str">
-        <f aca="false">IF($C11="","",IF($N11&gt;$D11,"工时超出","√"))</f>
+        <f aca="false">IF($C11="","",IF($D11=0,"缺总工时",IF(ROUND($N11-$D11,2)&gt;0,"工时超出","√")))</f>
         <v>√</v>
       </c>
       <c r="Q11" s="8"/>
@@ -2227,7 +2266,7 @@
         <v/>
       </c>
       <c r="P12" s="21" t="str">
-        <f aca="false">IF($C12="","",IF($N12&gt;$D12,"工时超出","√"))</f>
+        <f aca="false">IF($C12="","",IF($D12=0,"缺总工时",IF(ROUND($N12-$D12,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="Q12" s="8"/>
@@ -2259,7 +2298,7 @@
         <v/>
       </c>
       <c r="P13" s="21" t="str">
-        <f aca="false">IF($C13="","",IF($N13&gt;$D13,"工时超出","√"))</f>
+        <f aca="false">IF($C13="","",IF($D13=0,"缺总工时",IF(ROUND($N13-$D13,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="Q13" s="8"/>
@@ -2291,7 +2330,7 @@
         <v/>
       </c>
       <c r="P14" s="21" t="str">
-        <f aca="false">IF($C14="","",IF($N14&gt;$D14,"工时超出","√"))</f>
+        <f aca="false">IF($C14="","",IF($D14=0,"缺总工时",IF(ROUND($N14-$D14,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="Q14" s="8"/>
@@ -2323,7 +2362,7 @@
         <v/>
       </c>
       <c r="P15" s="21" t="str">
-        <f aca="false">IF($C15="","",IF($N15&gt;$D15,"工时超出","√"))</f>
+        <f aca="false">IF($C15="","",IF($D15=0,"缺总工时",IF(ROUND($N15-$D15,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="Q15" s="8"/>
@@ -2355,7 +2394,7 @@
         <v/>
       </c>
       <c r="P16" s="21" t="str">
-        <f aca="false">IF($C16="","",IF($N16&gt;$D16,"工时超出","√"))</f>
+        <f aca="false">IF($C16="","",IF($D16=0,"缺总工时",IF(ROUND($N16-$D16,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="Q16" s="8"/>
@@ -2387,7 +2426,7 @@
         <v/>
       </c>
       <c r="P17" s="21" t="str">
-        <f aca="false">IF($C17="","",IF($N17&gt;$D17,"工时超出","√"))</f>
+        <f aca="false">IF($C17="","",IF($D17=0,"缺总工时",IF(ROUND($N17-$D17,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="Q17" s="8"/>
@@ -2419,7 +2458,7 @@
         <v/>
       </c>
       <c r="P18" s="21" t="str">
-        <f aca="false">IF($C18="","",IF($N18&gt;$D18,"工时超出","√"))</f>
+        <f aca="false">IF($C18="","",IF($D18=0,"缺总工时",IF(ROUND($N18-$D18,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="Q18" s="8"/>
@@ -2451,7 +2490,7 @@
         <v/>
       </c>
       <c r="P19" s="21" t="str">
-        <f aca="false">IF($C19="","",IF($N19&gt;$D19,"工时超出","√"))</f>
+        <f aca="false">IF($C19="","",IF($D19=0,"缺总工时",IF(ROUND($N19-$D19,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="Q19" s="8"/>
@@ -2483,7 +2522,7 @@
         <v/>
       </c>
       <c r="P20" s="21" t="str">
-        <f aca="false">IF($C20="","",IF($N20&gt;$D20,"工时超出","√"))</f>
+        <f aca="false">IF($C20="","",IF($D20=0,"缺总工时",IF(ROUND($N20-$D20,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="Q20" s="8"/>
@@ -2515,7 +2554,7 @@
         <v/>
       </c>
       <c r="P21" s="21" t="str">
-        <f aca="false">IF($C21="","",IF($N21&gt;$D21,"工时超出","√"))</f>
+        <f aca="false">IF($C21="","",IF($D21=0,"缺总工时",IF(ROUND($N21-$D21,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="Q21" s="8"/>
@@ -2547,7 +2586,7 @@
         <v/>
       </c>
       <c r="P22" s="21" t="str">
-        <f aca="false">IF($C22="","",IF($N22&gt;$D22,"工时超出","√"))</f>
+        <f aca="false">IF($C22="","",IF($D22=0,"缺总工时",IF(ROUND($N22-$D22,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="Q22" s="8"/>
@@ -2579,7 +2618,7 @@
         <v/>
       </c>
       <c r="P23" s="21" t="str">
-        <f aca="false">IF($C23="","",IF($N23&gt;$D23,"工时超出","√"))</f>
+        <f aca="false">IF($C23="","",IF($D23=0,"缺总工时",IF(ROUND($N23-$D23,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="Q23" s="8"/>
@@ -2611,7 +2650,7 @@
         <v/>
       </c>
       <c r="P24" s="21" t="str">
-        <f aca="false">IF($C24="","",IF($N24&gt;$D24,"工时超出","√"))</f>
+        <f aca="false">IF($C24="","",IF($D24=0,"缺总工时",IF(ROUND($N24-$D24,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="Q24" s="8"/>
@@ -2643,7 +2682,7 @@
         <v/>
       </c>
       <c r="P25" s="21" t="str">
-        <f aca="false">IF($C25="","",IF($N25&gt;$D25,"工时超出","√"))</f>
+        <f aca="false">IF($C25="","",IF($D25=0,"缺总工时",IF(ROUND($N25-$D25,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="Q25" s="8"/>
@@ -2675,14 +2714,14 @@
         <v/>
       </c>
       <c r="P26" s="21" t="str">
-        <f aca="false">IF($C26="","",IF($N26&gt;$D26,"工时超出","√"))</f>
+        <f aca="false">IF($C26="","",IF($D26=0,"缺总工时",IF(ROUND($N26-$D26,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="Q26" s="8"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C27" s="22"/>
       <c r="D27" s="23" t="n">
@@ -2738,15 +2777,15 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D29" s="26" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M29" s="26" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="156.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -2793,7 +2832,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
@@ -2814,7 +2853,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P3" s="12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q3" s="13" t="n">
         <v>46266</v>
@@ -2823,22 +2862,22 @@
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H4" s="15"/>
       <c r="I4" s="15"/>
@@ -2849,13 +2888,13 @@
       <c r="N4" s="15"/>
       <c r="O4" s="15"/>
       <c r="P4" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q4" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R4" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2897,10 +2936,10 @@
         <v>RD08</v>
       </c>
       <c r="O5" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P5" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q5" s="14"/>
       <c r="R5" s="14"/>
@@ -2953,10 +2992,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E7" s="18" t="n">
         <v>180</v>
@@ -2990,11 +3029,11 @@
         <v>0.8</v>
       </c>
       <c r="Q7" s="21" t="str">
-        <f aca="false">IF($C7="","",IF($O7&gt;$E7,"工时超出","√"))</f>
+        <f aca="false">IF($C7="","",IF($E7=0,"缺总工时",IF(ROUND($O7-$E7,2)&gt;0,"工时超出","√")))</f>
         <v>√</v>
       </c>
       <c r="R7" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3002,10 +3041,10 @@
         <v>2</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E8" s="18" t="n">
         <v>180</v>
@@ -3037,11 +3076,11 @@
         <v>0.6</v>
       </c>
       <c r="Q8" s="21" t="str">
-        <f aca="false">IF($C8="","",IF($O8&gt;$E8,"工时超出","√"))</f>
+        <f aca="false">IF($C8="","",IF($E8=0,"缺总工时",IF(ROUND($O8-$E8,2)&gt;0,"工时超出","√")))</f>
         <v>√</v>
       </c>
       <c r="R8" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3049,10 +3088,10 @@
         <v>3</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E9" s="18" t="n">
         <v>180</v>
@@ -3086,11 +3125,11 @@
         <v>0.8</v>
       </c>
       <c r="Q9" s="21" t="str">
-        <f aca="false">IF($C9="","",IF($O9&gt;$E9,"工时超出","√"))</f>
+        <f aca="false">IF($C9="","",IF($E9=0,"缺总工时",IF(ROUND($O9-$E9,2)&gt;0,"工时超出","√")))</f>
         <v>√</v>
       </c>
       <c r="R9" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3098,10 +3137,10 @@
         <v>4</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E10" s="18" t="n">
         <v>180</v>
@@ -3133,11 +3172,11 @@
         <v>0.6</v>
       </c>
       <c r="Q10" s="21" t="str">
-        <f aca="false">IF($C10="","",IF($O10&gt;$E10,"工时超出","√"))</f>
+        <f aca="false">IF($C10="","",IF($E10=0,"缺总工时",IF(ROUND($O10-$E10,2)&gt;0,"工时超出","√")))</f>
         <v>√</v>
       </c>
       <c r="R10" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3145,10 +3184,10 @@
         <v>5</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E11" s="18" t="n">
         <v>180</v>
@@ -3178,11 +3217,11 @@
         <v>0.4</v>
       </c>
       <c r="Q11" s="21" t="str">
-        <f aca="false">IF($C11="","",IF($O11&gt;$E11,"工时超出","√"))</f>
+        <f aca="false">IF($C11="","",IF($E11=0,"缺总工时",IF(ROUND($O11-$E11,2)&gt;0,"工时超出","√")))</f>
         <v>√</v>
       </c>
       <c r="R11" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3190,10 +3229,10 @@
         <v>6</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E12" s="18" t="n">
         <v>180</v>
@@ -3221,11 +3260,11 @@
         <v>0.2</v>
       </c>
       <c r="Q12" s="21" t="str">
-        <f aca="false">IF($C12="","",IF($O12&gt;$E12,"工时超出","√"))</f>
+        <f aca="false">IF($C12="","",IF($E12=0,"缺总工时",IF(ROUND($O12-$E12,2)&gt;0,"工时超出","√")))</f>
         <v>√</v>
       </c>
       <c r="R12" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3233,10 +3272,10 @@
         <v>7</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E13" s="18" t="n">
         <v>180</v>
@@ -3264,11 +3303,11 @@
         <v>0.2</v>
       </c>
       <c r="Q13" s="21" t="str">
-        <f aca="false">IF($C13="","",IF($O13&gt;$E13,"工时超出","√"))</f>
+        <f aca="false">IF($C13="","",IF($E13=0,"缺总工时",IF(ROUND($O13-$E13,2)&gt;0,"工时超出","√")))</f>
         <v>√</v>
       </c>
       <c r="R13" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3276,10 +3315,10 @@
         <v>8</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E14" s="18" t="n">
         <v>180</v>
@@ -3305,11 +3344,11 @@
         <v>0</v>
       </c>
       <c r="Q14" s="21" t="str">
-        <f aca="false">IF($C14="","",IF($O14&gt;$E14,"工时超出","√"))</f>
+        <f aca="false">IF($C14="","",IF($E14=0,"缺总工时",IF(ROUND($O14-$E14,2)&gt;0,"工时超出","√")))</f>
         <v>√</v>
       </c>
       <c r="R14" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3317,10 +3356,10 @@
         <v>9</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E15" s="18" t="n">
         <v>180</v>
@@ -3348,11 +3387,11 @@
         <v>0.2</v>
       </c>
       <c r="Q15" s="21" t="str">
-        <f aca="false">IF($C15="","",IF($O15&gt;$E15,"工时超出","√"))</f>
+        <f aca="false">IF($C15="","",IF($E15=0,"缺总工时",IF(ROUND($O15-$E15,2)&gt;0,"工时超出","√")))</f>
         <v>√</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3360,10 +3399,10 @@
         <v>10</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E16" s="18" t="n">
         <v>180</v>
@@ -3391,11 +3430,11 @@
         <v>0.2</v>
       </c>
       <c r="Q16" s="21" t="str">
-        <f aca="false">IF($C16="","",IF($O16&gt;$E16,"工时超出","√"))</f>
+        <f aca="false">IF($C16="","",IF($E16=0,"缺总工时",IF(ROUND($O16-$E16,2)&gt;0,"工时超出","√")))</f>
         <v>√</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3403,10 +3442,10 @@
         <v>11</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E17" s="18" t="n">
         <v>180</v>
@@ -3442,11 +3481,11 @@
         <v>1</v>
       </c>
       <c r="Q17" s="21" t="str">
-        <f aca="false">IF($C17="","",IF($O17&gt;$E17,"工时超出","√"))</f>
+        <f aca="false">IF($C17="","",IF($E17=0,"缺总工时",IF(ROUND($O17-$E17,2)&gt;0,"工时超出","√")))</f>
         <v>√</v>
       </c>
       <c r="R17" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3477,7 +3516,7 @@
         <v/>
       </c>
       <c r="Q18" s="21" t="str">
-        <f aca="false">IF($C18="","",IF($O18&gt;$E18,"工时超出","√"))</f>
+        <f aca="false">IF($C18="","",IF($E18=0,"缺总工时",IF(ROUND($O18-$E18,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="R18" s="27"/>
@@ -3510,7 +3549,7 @@
         <v/>
       </c>
       <c r="Q19" s="21" t="str">
-        <f aca="false">IF($C19="","",IF($O19&gt;$E19,"工时超出","√"))</f>
+        <f aca="false">IF($C19="","",IF($E19=0,"缺总工时",IF(ROUND($O19-$E19,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="R19" s="27"/>
@@ -3543,7 +3582,7 @@
         <v/>
       </c>
       <c r="Q20" s="21" t="str">
-        <f aca="false">IF($C20="","",IF($O20&gt;$E20,"工时超出","√"))</f>
+        <f aca="false">IF($C20="","",IF($E20=0,"缺总工时",IF(ROUND($O20-$E20,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="R20" s="27"/>
@@ -3576,7 +3615,7 @@
         <v/>
       </c>
       <c r="Q21" s="21" t="str">
-        <f aca="false">IF($C21="","",IF($O21&gt;$E21,"工时超出","√"))</f>
+        <f aca="false">IF($C21="","",IF($E21=0,"缺总工时",IF(ROUND($O21-$E21,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="R21" s="27"/>
@@ -3609,7 +3648,7 @@
         <v/>
       </c>
       <c r="Q22" s="21" t="str">
-        <f aca="false">IF($C22="","",IF($O22&gt;$E22,"工时超出","√"))</f>
+        <f aca="false">IF($C22="","",IF($E22=0,"缺总工时",IF(ROUND($O22-$E22,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="R22" s="27"/>
@@ -3642,7 +3681,7 @@
         <v/>
       </c>
       <c r="Q23" s="21" t="str">
-        <f aca="false">IF($C23="","",IF($O23&gt;$E23,"工时超出","√"))</f>
+        <f aca="false">IF($C23="","",IF($E23=0,"缺总工时",IF(ROUND($O23-$E23,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="R23" s="27"/>
@@ -3675,7 +3714,7 @@
         <v/>
       </c>
       <c r="Q24" s="21" t="str">
-        <f aca="false">IF($C24="","",IF($O24&gt;$E24,"工时超出","√"))</f>
+        <f aca="false">IF($C24="","",IF($E24=0,"缺总工时",IF(ROUND($O24-$E24,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="R24" s="27"/>
@@ -3708,7 +3747,7 @@
         <v/>
       </c>
       <c r="Q25" s="21" t="str">
-        <f aca="false">IF($C25="","",IF($O25&gt;$E25,"工时超出","√"))</f>
+        <f aca="false">IF($C25="","",IF($E25=0,"缺总工时",IF(ROUND($O25-$E25,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="R25" s="27"/>
@@ -3741,7 +3780,7 @@
         <v/>
       </c>
       <c r="Q26" s="21" t="str">
-        <f aca="false">IF($C26="","",IF($O26&gt;$E26,"工时超出","√"))</f>
+        <f aca="false">IF($C26="","",IF($E26=0,"缺总工时",IF(ROUND($O26-$E26,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="R26" s="27"/>
@@ -3774,7 +3813,7 @@
         <v/>
       </c>
       <c r="Q27" s="21" t="str">
-        <f aca="false">IF($C27="","",IF($O27&gt;$E27,"工时超出","√"))</f>
+        <f aca="false">IF($C27="","",IF($E27=0,"缺总工时",IF(ROUND($O27-$E27,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="R27" s="27"/>
@@ -3807,7 +3846,7 @@
         <v/>
       </c>
       <c r="Q28" s="21" t="str">
-        <f aca="false">IF($C28="","",IF($O28&gt;$E28,"工时超出","√"))</f>
+        <f aca="false">IF($C28="","",IF($E28=0,"缺总工时",IF(ROUND($O28-$E28,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="R28" s="27"/>
@@ -3840,7 +3879,7 @@
         <v/>
       </c>
       <c r="Q29" s="21" t="str">
-        <f aca="false">IF($C29="","",IF($O29&gt;$E29,"工时超出","√"))</f>
+        <f aca="false">IF($C29="","",IF($E29=0,"缺总工时",IF(ROUND($O29-$E29,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="R29" s="27"/>
@@ -3873,7 +3912,7 @@
         <v/>
       </c>
       <c r="Q30" s="21" t="str">
-        <f aca="false">IF($C30="","",IF($O30&gt;$E30,"工时超出","√"))</f>
+        <f aca="false">IF($C30="","",IF($E30=0,"缺总工时",IF(ROUND($O30-$E30,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="R30" s="27"/>
@@ -3906,14 +3945,14 @@
         <v/>
       </c>
       <c r="Q31" s="21" t="str">
-        <f aca="false">IF($C31="","",IF($O31&gt;$E31,"工时超出","√"))</f>
+        <f aca="false">IF($C31="","",IF($E31=0,"缺总工时",IF(ROUND($O31-$E31,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="R31" s="27"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C32" s="22"/>
       <c r="D32" s="22"/>
@@ -3970,15 +4009,15 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E34" s="26" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N34" s="26" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="156.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -4026,7 +4065,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
@@ -4047,7 +4086,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P3" s="12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q3" s="13" t="n">
         <v>46266</v>
@@ -4056,22 +4095,22 @@
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H4" s="15"/>
       <c r="I4" s="15"/>
@@ -4082,13 +4121,13 @@
       <c r="N4" s="15"/>
       <c r="O4" s="15"/>
       <c r="P4" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q4" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R4" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4130,10 +4169,10 @@
         <v>RD08</v>
       </c>
       <c r="O5" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P5" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q5" s="14"/>
       <c r="R5" s="14"/>
@@ -4186,10 +4225,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E7" s="18" t="n">
         <v>180</v>
@@ -4223,7 +4262,7 @@
         <v>0.8</v>
       </c>
       <c r="Q7" s="21" t="str">
-        <f aca="false">IF($C7="","",IF($O7&gt;$E7,"工时超出","√"))</f>
+        <f aca="false">IF($C7="","",IF($E7=0,"缺总工时",IF(ROUND($O7-$E7,2)&gt;0,"工时超出","√")))</f>
         <v>√</v>
       </c>
       <c r="R7" s="27"/>
@@ -4233,10 +4272,10 @@
         <v>2</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E8" s="18" t="n">
         <v>180</v>
@@ -4270,7 +4309,7 @@
         <v>0.8</v>
       </c>
       <c r="Q8" s="21" t="str">
-        <f aca="false">IF($C8="","",IF($O8&gt;$E8,"工时超出","√"))</f>
+        <f aca="false">IF($C8="","",IF($E8=0,"缺总工时",IF(ROUND($O8-$E8,2)&gt;0,"工时超出","√")))</f>
         <v>√</v>
       </c>
       <c r="R8" s="27"/>
@@ -4280,10 +4319,10 @@
         <v>3</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E9" s="18" t="n">
         <v>180</v>
@@ -4315,7 +4354,7 @@
         <v>0.6</v>
       </c>
       <c r="Q9" s="21" t="str">
-        <f aca="false">IF($C9="","",IF($O9&gt;$E9,"工时超出","√"))</f>
+        <f aca="false">IF($C9="","",IF($E9=0,"缺总工时",IF(ROUND($O9-$E9,2)&gt;0,"工时超出","√")))</f>
         <v>√</v>
       </c>
       <c r="R9" s="27"/>
@@ -4325,10 +4364,10 @@
         <v>4</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E10" s="18" t="n">
         <v>180</v>
@@ -4358,7 +4397,7 @@
         <v>0.4</v>
       </c>
       <c r="Q10" s="21" t="str">
-        <f aca="false">IF($C10="","",IF($O10&gt;$E10,"工时超出","√"))</f>
+        <f aca="false">IF($C10="","",IF($E10=0,"缺总工时",IF(ROUND($O10-$E10,2)&gt;0,"工时超出","√")))</f>
         <v>√</v>
       </c>
       <c r="R10" s="27"/>
@@ -4368,10 +4407,10 @@
         <v>5</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E11" s="18" t="n">
         <v>180</v>
@@ -4401,7 +4440,7 @@
         <v>0.4</v>
       </c>
       <c r="Q11" s="21" t="str">
-        <f aca="false">IF($C11="","",IF($O11&gt;$E11,"工时超出","√"))</f>
+        <f aca="false">IF($C11="","",IF($E11=0,"缺总工时",IF(ROUND($O11-$E11,2)&gt;0,"工时超出","√")))</f>
         <v>√</v>
       </c>
       <c r="R11" s="27"/>
@@ -4411,10 +4450,10 @@
         <v>6</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E12" s="18" t="n">
         <v>180</v>
@@ -4442,7 +4481,7 @@
         <v>0.2</v>
       </c>
       <c r="Q12" s="21" t="str">
-        <f aca="false">IF($C12="","",IF($O12&gt;$E12,"工时超出","√"))</f>
+        <f aca="false">IF($C12="","",IF($E12=0,"缺总工时",IF(ROUND($O12-$E12,2)&gt;0,"工时超出","√")))</f>
         <v>√</v>
       </c>
       <c r="R12" s="27"/>
@@ -4475,7 +4514,7 @@
         <v/>
       </c>
       <c r="Q13" s="21" t="str">
-        <f aca="false">IF($C13="","",IF($O13&gt;$E13,"工时超出","√"))</f>
+        <f aca="false">IF($C13="","",IF($E13=0,"缺总工时",IF(ROUND($O13-$E13,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="R13" s="27"/>
@@ -4508,7 +4547,7 @@
         <v/>
       </c>
       <c r="Q14" s="21" t="str">
-        <f aca="false">IF($C14="","",IF($O14&gt;$E14,"工时超出","√"))</f>
+        <f aca="false">IF($C14="","",IF($E14=0,"缺总工时",IF(ROUND($O14-$E14,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="R14" s="27"/>
@@ -4541,7 +4580,7 @@
         <v/>
       </c>
       <c r="Q15" s="21" t="str">
-        <f aca="false">IF($C15="","",IF($O15&gt;$E15,"工时超出","√"))</f>
+        <f aca="false">IF($C15="","",IF($E15=0,"缺总工时",IF(ROUND($O15-$E15,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="R15" s="27"/>
@@ -4574,7 +4613,7 @@
         <v/>
       </c>
       <c r="Q16" s="21" t="str">
-        <f aca="false">IF($C16="","",IF($O16&gt;$E16,"工时超出","√"))</f>
+        <f aca="false">IF($C16="","",IF($E16=0,"缺总工时",IF(ROUND($O16-$E16,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="R16" s="27"/>
@@ -4607,7 +4646,7 @@
         <v/>
       </c>
       <c r="Q17" s="21" t="str">
-        <f aca="false">IF($C17="","",IF($O17&gt;$E17,"工时超出","√"))</f>
+        <f aca="false">IF($C17="","",IF($E17=0,"缺总工时",IF(ROUND($O17-$E17,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="R17" s="27"/>
@@ -4640,7 +4679,7 @@
         <v/>
       </c>
       <c r="Q18" s="21" t="str">
-        <f aca="false">IF($C18="","",IF($O18&gt;$E18,"工时超出","√"))</f>
+        <f aca="false">IF($C18="","",IF($E18=0,"缺总工时",IF(ROUND($O18-$E18,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="R18" s="27"/>
@@ -4673,7 +4712,7 @@
         <v/>
       </c>
       <c r="Q19" s="21" t="str">
-        <f aca="false">IF($C19="","",IF($O19&gt;$E19,"工时超出","√"))</f>
+        <f aca="false">IF($C19="","",IF($E19=0,"缺总工时",IF(ROUND($O19-$E19,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="R19" s="27"/>
@@ -4706,7 +4745,7 @@
         <v/>
       </c>
       <c r="Q20" s="21" t="str">
-        <f aca="false">IF($C20="","",IF($O20&gt;$E20,"工时超出","√"))</f>
+        <f aca="false">IF($C20="","",IF($E20=0,"缺总工时",IF(ROUND($O20-$E20,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="R20" s="27"/>
@@ -4739,7 +4778,7 @@
         <v/>
       </c>
       <c r="Q21" s="21" t="str">
-        <f aca="false">IF($C21="","",IF($O21&gt;$E21,"工时超出","√"))</f>
+        <f aca="false">IF($C21="","",IF($E21=0,"缺总工时",IF(ROUND($O21-$E21,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="R21" s="27"/>
@@ -4772,7 +4811,7 @@
         <v/>
       </c>
       <c r="Q22" s="21" t="str">
-        <f aca="false">IF($C22="","",IF($O22&gt;$E22,"工时超出","√"))</f>
+        <f aca="false">IF($C22="","",IF($E22=0,"缺总工时",IF(ROUND($O22-$E22,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="R22" s="27"/>
@@ -4805,7 +4844,7 @@
         <v/>
       </c>
       <c r="Q23" s="21" t="str">
-        <f aca="false">IF($C23="","",IF($O23&gt;$E23,"工时超出","√"))</f>
+        <f aca="false">IF($C23="","",IF($E23=0,"缺总工时",IF(ROUND($O23-$E23,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="R23" s="27"/>
@@ -4838,7 +4877,7 @@
         <v/>
       </c>
       <c r="Q24" s="21" t="str">
-        <f aca="false">IF($C24="","",IF($O24&gt;$E24,"工时超出","√"))</f>
+        <f aca="false">IF($C24="","",IF($E24=0,"缺总工时",IF(ROUND($O24-$E24,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="R24" s="27"/>
@@ -4871,7 +4910,7 @@
         <v/>
       </c>
       <c r="Q25" s="21" t="str">
-        <f aca="false">IF($C25="","",IF($O25&gt;$E25,"工时超出","√"))</f>
+        <f aca="false">IF($C25="","",IF($E25=0,"缺总工时",IF(ROUND($O25-$E25,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="R25" s="27"/>
@@ -4904,14 +4943,14 @@
         <v/>
       </c>
       <c r="Q26" s="21" t="str">
-        <f aca="false">IF($C26="","",IF($O26&gt;$E26,"工时超出","√"))</f>
+        <f aca="false">IF($C26="","",IF($E26=0,"缺总工时",IF(ROUND($O26-$E26,2)&gt;0,"工时超出","√")))</f>
         <v/>
       </c>
       <c r="R26" s="27"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C27" s="22"/>
       <c r="D27" s="22"/>
@@ -4968,15 +5007,15 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E29" s="26" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N29" s="26" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="156.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -5010,7 +5049,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:Q126"/>
+  <dimension ref="B2:R126"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -5019,11 +5058,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="5" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="11"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -5040,33 +5080,34 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P3" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H4" s="15"/>
       <c r="I4" s="15"/>
@@ -5077,10 +5118,13 @@
       <c r="N4" s="15"/>
       <c r="O4" s="15"/>
       <c r="P4" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q4" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R4" s="14" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5122,12 +5166,13 @@
         <v>RD08</v>
       </c>
       <c r="O5" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P5" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q5" s="14"/>
+      <c r="R5" s="14"/>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="14"/>
@@ -5170,6 +5215,7 @@
       <c r="O6" s="14"/>
       <c r="P6" s="14"/>
       <c r="Q6" s="14"/>
+      <c r="R6" s="14"/>
     </row>
     <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="28" t="n">
@@ -5179,7 +5225,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7" s="18" t="n">
         <v>172.5</v>
@@ -5211,7 +5257,11 @@
         <v>0.753623188405797</v>
       </c>
       <c r="Q7" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R7" s="21" t="str">
+        <f aca="false">IF($D7="","",IF($B7="","缺月份",IF($E7=0,"缺总工时",IF(ROUND($O7-$E7,2)&gt;0,"工时超出","√"))))</f>
+        <v>√</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5222,7 +5272,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8" s="18" t="n">
         <v>172.5</v>
@@ -5252,6 +5302,10 @@
         <v>0.63768115942029</v>
       </c>
       <c r="Q8" s="27"/>
+      <c r="R8" s="21" t="str">
+        <f aca="false">IF($D8="","",IF($B8="","缺月份",IF($E8=0,"缺总工时",IF(ROUND($O8-$E8,2)&gt;0,"工时超出","√"))))</f>
+        <v>√</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="28" t="n">
@@ -5261,7 +5315,7 @@
         <v>3</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E9" s="18" t="n">
         <v>172.5</v>
@@ -5293,6 +5347,10 @@
         <v>0.695652173913044</v>
       </c>
       <c r="Q9" s="27"/>
+      <c r="R9" s="21" t="str">
+        <f aca="false">IF($D9="","",IF($B9="","缺月份",IF($E9=0,"缺总工时",IF(ROUND($O9-$E9,2)&gt;0,"工时超出","√"))))</f>
+        <v>√</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="28" t="n">
@@ -5302,7 +5360,7 @@
         <v>4</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E10" s="18" t="n">
         <v>172.5</v>
@@ -5332,6 +5390,10 @@
         <v>0.695652173913044</v>
       </c>
       <c r="Q10" s="27"/>
+      <c r="R10" s="21" t="str">
+        <f aca="false">IF($D10="","",IF($B10="","缺月份",IF($E10=0,"缺总工时",IF(ROUND($O10-$E10,2)&gt;0,"工时超出","√"))))</f>
+        <v>√</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="28" t="n">
@@ -5341,7 +5403,7 @@
         <v>5</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E11" s="18" t="n">
         <v>172.5</v>
@@ -5373,6 +5435,10 @@
         <v>0.811594202898551</v>
       </c>
       <c r="Q11" s="27"/>
+      <c r="R11" s="21" t="str">
+        <f aca="false">IF($D11="","",IF($B11="","缺月份",IF($E11=0,"缺总工时",IF(ROUND($O11-$E11,2)&gt;0,"工时超出","√"))))</f>
+        <v>√</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="28"/>
@@ -5400,6 +5466,10 @@
         <v/>
       </c>
       <c r="Q12" s="27"/>
+      <c r="R12" s="21" t="str">
+        <f aca="false">IF($D12="","",IF($B12="","缺月份",IF($E12=0,"缺总工时",IF(ROUND($O12-$E12,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="28"/>
@@ -5427,6 +5497,10 @@
         <v/>
       </c>
       <c r="Q13" s="27"/>
+      <c r="R13" s="21" t="str">
+        <f aca="false">IF($D13="","",IF($B13="","缺月份",IF($E13=0,"缺总工时",IF(ROUND($O13-$E13,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="28"/>
@@ -5454,6 +5528,10 @@
         <v/>
       </c>
       <c r="Q14" s="27"/>
+      <c r="R14" s="21" t="str">
+        <f aca="false">IF($D14="","",IF($B14="","缺月份",IF($E14=0,"缺总工时",IF(ROUND($O14-$E14,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="28"/>
@@ -5481,6 +5559,10 @@
         <v/>
       </c>
       <c r="Q15" s="27"/>
+      <c r="R15" s="21" t="str">
+        <f aca="false">IF($D15="","",IF($B15="","缺月份",IF($E15=0,"缺总工时",IF(ROUND($O15-$E15,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="28"/>
@@ -5508,6 +5590,10 @@
         <v/>
       </c>
       <c r="Q16" s="27"/>
+      <c r="R16" s="21" t="str">
+        <f aca="false">IF($D16="","",IF($B16="","缺月份",IF($E16=0,"缺总工时",IF(ROUND($O16-$E16,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="28"/>
@@ -5535,6 +5621,10 @@
         <v/>
       </c>
       <c r="Q17" s="27"/>
+      <c r="R17" s="21" t="str">
+        <f aca="false">IF($D17="","",IF($B17="","缺月份",IF($E17=0,"缺总工时",IF(ROUND($O17-$E17,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="28"/>
@@ -5562,6 +5652,10 @@
         <v/>
       </c>
       <c r="Q18" s="27"/>
+      <c r="R18" s="21" t="str">
+        <f aca="false">IF($D18="","",IF($B18="","缺月份",IF($E18=0,"缺总工时",IF(ROUND($O18-$E18,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="28"/>
@@ -5589,6 +5683,10 @@
         <v/>
       </c>
       <c r="Q19" s="27"/>
+      <c r="R19" s="21" t="str">
+        <f aca="false">IF($D19="","",IF($B19="","缺月份",IF($E19=0,"缺总工时",IF(ROUND($O19-$E19,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="28"/>
@@ -5616,6 +5714,10 @@
         <v/>
       </c>
       <c r="Q20" s="27"/>
+      <c r="R20" s="21" t="str">
+        <f aca="false">IF($D20="","",IF($B20="","缺月份",IF($E20=0,"缺总工时",IF(ROUND($O20-$E20,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="28"/>
@@ -5643,6 +5745,10 @@
         <v/>
       </c>
       <c r="Q21" s="27"/>
+      <c r="R21" s="21" t="str">
+        <f aca="false">IF($D21="","",IF($B21="","缺月份",IF($E21=0,"缺总工时",IF(ROUND($O21-$E21,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="28"/>
@@ -5670,6 +5776,10 @@
         <v/>
       </c>
       <c r="Q22" s="27"/>
+      <c r="R22" s="21" t="str">
+        <f aca="false">IF($D22="","",IF($B22="","缺月份",IF($E22=0,"缺总工时",IF(ROUND($O22-$E22,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="28"/>
@@ -5697,6 +5807,10 @@
         <v/>
       </c>
       <c r="Q23" s="27"/>
+      <c r="R23" s="21" t="str">
+        <f aca="false">IF($D23="","",IF($B23="","缺月份",IF($E23=0,"缺总工时",IF(ROUND($O23-$E23,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="28"/>
@@ -5724,6 +5838,10 @@
         <v/>
       </c>
       <c r="Q24" s="27"/>
+      <c r="R24" s="21" t="str">
+        <f aca="false">IF($D24="","",IF($B24="","缺月份",IF($E24=0,"缺总工时",IF(ROUND($O24-$E24,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="28"/>
@@ -5751,6 +5869,10 @@
         <v/>
       </c>
       <c r="Q25" s="27"/>
+      <c r="R25" s="21" t="str">
+        <f aca="false">IF($D25="","",IF($B25="","缺月份",IF($E25=0,"缺总工时",IF(ROUND($O25-$E25,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="28"/>
@@ -5778,6 +5900,10 @@
         <v/>
       </c>
       <c r="Q26" s="27"/>
+      <c r="R26" s="21" t="str">
+        <f aca="false">IF($D26="","",IF($B26="","缺月份",IF($E26=0,"缺总工时",IF(ROUND($O26-$E26,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="28"/>
@@ -5805,6 +5931,10 @@
         <v/>
       </c>
       <c r="Q27" s="27"/>
+      <c r="R27" s="21" t="str">
+        <f aca="false">IF($D27="","",IF($B27="","缺月份",IF($E27=0,"缺总工时",IF(ROUND($O27-$E27,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="28"/>
@@ -5832,6 +5962,10 @@
         <v/>
       </c>
       <c r="Q28" s="27"/>
+      <c r="R28" s="21" t="str">
+        <f aca="false">IF($D28="","",IF($B28="","缺月份",IF($E28=0,"缺总工时",IF(ROUND($O28-$E28,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="28"/>
@@ -5859,6 +5993,10 @@
         <v/>
       </c>
       <c r="Q29" s="27"/>
+      <c r="R29" s="21" t="str">
+        <f aca="false">IF($D29="","",IF($B29="","缺月份",IF($E29=0,"缺总工时",IF(ROUND($O29-$E29,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="28"/>
@@ -5886,6 +6024,10 @@
         <v/>
       </c>
       <c r="Q30" s="27"/>
+      <c r="R30" s="21" t="str">
+        <f aca="false">IF($D30="","",IF($B30="","缺月份",IF($E30=0,"缺总工时",IF(ROUND($O30-$E30,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="28"/>
@@ -5913,6 +6055,10 @@
         <v/>
       </c>
       <c r="Q31" s="27"/>
+      <c r="R31" s="21" t="str">
+        <f aca="false">IF($D31="","",IF($B31="","缺月份",IF($E31=0,"缺总工时",IF(ROUND($O31-$E31,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="28"/>
@@ -5940,6 +6086,10 @@
         <v/>
       </c>
       <c r="Q32" s="27"/>
+      <c r="R32" s="21" t="str">
+        <f aca="false">IF($D32="","",IF($B32="","缺月份",IF($E32=0,"缺总工时",IF(ROUND($O32-$E32,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="28"/>
@@ -5967,6 +6117,10 @@
         <v/>
       </c>
       <c r="Q33" s="27"/>
+      <c r="R33" s="21" t="str">
+        <f aca="false">IF($D33="","",IF($B33="","缺月份",IF($E33=0,"缺总工时",IF(ROUND($O33-$E33,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="28"/>
@@ -5994,6 +6148,10 @@
         <v/>
       </c>
       <c r="Q34" s="27"/>
+      <c r="R34" s="21" t="str">
+        <f aca="false">IF($D34="","",IF($B34="","缺月份",IF($E34=0,"缺总工时",IF(ROUND($O34-$E34,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="28"/>
@@ -6021,6 +6179,10 @@
         <v/>
       </c>
       <c r="Q35" s="27"/>
+      <c r="R35" s="21" t="str">
+        <f aca="false">IF($D35="","",IF($B35="","缺月份",IF($E35=0,"缺总工时",IF(ROUND($O35-$E35,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="28"/>
@@ -6048,6 +6210,10 @@
         <v/>
       </c>
       <c r="Q36" s="27"/>
+      <c r="R36" s="21" t="str">
+        <f aca="false">IF($D36="","",IF($B36="","缺月份",IF($E36=0,"缺总工时",IF(ROUND($O36-$E36,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="28"/>
@@ -6075,6 +6241,10 @@
         <v/>
       </c>
       <c r="Q37" s="27"/>
+      <c r="R37" s="21" t="str">
+        <f aca="false">IF($D37="","",IF($B37="","缺月份",IF($E37=0,"缺总工时",IF(ROUND($O37-$E37,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="28"/>
@@ -6102,6 +6272,10 @@
         <v/>
       </c>
       <c r="Q38" s="27"/>
+      <c r="R38" s="21" t="str">
+        <f aca="false">IF($D38="","",IF($B38="","缺月份",IF($E38=0,"缺总工时",IF(ROUND($O38-$E38,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="28"/>
@@ -6129,6 +6303,10 @@
         <v/>
       </c>
       <c r="Q39" s="27"/>
+      <c r="R39" s="21" t="str">
+        <f aca="false">IF($D39="","",IF($B39="","缺月份",IF($E39=0,"缺总工时",IF(ROUND($O39-$E39,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="28"/>
@@ -6156,6 +6334,10 @@
         <v/>
       </c>
       <c r="Q40" s="27"/>
+      <c r="R40" s="21" t="str">
+        <f aca="false">IF($D40="","",IF($B40="","缺月份",IF($E40=0,"缺总工时",IF(ROUND($O40-$E40,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="28"/>
@@ -6183,6 +6365,10 @@
         <v/>
       </c>
       <c r="Q41" s="27"/>
+      <c r="R41" s="21" t="str">
+        <f aca="false">IF($D41="","",IF($B41="","缺月份",IF($E41=0,"缺总工时",IF(ROUND($O41-$E41,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="28"/>
@@ -6210,6 +6396,10 @@
         <v/>
       </c>
       <c r="Q42" s="27"/>
+      <c r="R42" s="21" t="str">
+        <f aca="false">IF($D42="","",IF($B42="","缺月份",IF($E42=0,"缺总工时",IF(ROUND($O42-$E42,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="28"/>
@@ -6237,6 +6427,10 @@
         <v/>
       </c>
       <c r="Q43" s="27"/>
+      <c r="R43" s="21" t="str">
+        <f aca="false">IF($D43="","",IF($B43="","缺月份",IF($E43=0,"缺总工时",IF(ROUND($O43-$E43,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="28"/>
@@ -6264,6 +6458,10 @@
         <v/>
       </c>
       <c r="Q44" s="27"/>
+      <c r="R44" s="21" t="str">
+        <f aca="false">IF($D44="","",IF($B44="","缺月份",IF($E44=0,"缺总工时",IF(ROUND($O44-$E44,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="28"/>
@@ -6291,6 +6489,10 @@
         <v/>
       </c>
       <c r="Q45" s="27"/>
+      <c r="R45" s="21" t="str">
+        <f aca="false">IF($D45="","",IF($B45="","缺月份",IF($E45=0,"缺总工时",IF(ROUND($O45-$E45,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="28"/>
@@ -6318,6 +6520,10 @@
         <v/>
       </c>
       <c r="Q46" s="27"/>
+      <c r="R46" s="21" t="str">
+        <f aca="false">IF($D46="","",IF($B46="","缺月份",IF($E46=0,"缺总工时",IF(ROUND($O46-$E46,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="28"/>
@@ -6345,6 +6551,10 @@
         <v/>
       </c>
       <c r="Q47" s="27"/>
+      <c r="R47" s="21" t="str">
+        <f aca="false">IF($D47="","",IF($B47="","缺月份",IF($E47=0,"缺总工时",IF(ROUND($O47-$E47,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="28"/>
@@ -6372,6 +6582,10 @@
         <v/>
       </c>
       <c r="Q48" s="27"/>
+      <c r="R48" s="21" t="str">
+        <f aca="false">IF($D48="","",IF($B48="","缺月份",IF($E48=0,"缺总工时",IF(ROUND($O48-$E48,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="28"/>
@@ -6399,6 +6613,10 @@
         <v/>
       </c>
       <c r="Q49" s="27"/>
+      <c r="R49" s="21" t="str">
+        <f aca="false">IF($D49="","",IF($B49="","缺月份",IF($E49=0,"缺总工时",IF(ROUND($O49-$E49,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="28"/>
@@ -6426,6 +6644,10 @@
         <v/>
       </c>
       <c r="Q50" s="27"/>
+      <c r="R50" s="21" t="str">
+        <f aca="false">IF($D50="","",IF($B50="","缺月份",IF($E50=0,"缺总工时",IF(ROUND($O50-$E50,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="28"/>
@@ -6453,6 +6675,10 @@
         <v/>
       </c>
       <c r="Q51" s="27"/>
+      <c r="R51" s="21" t="str">
+        <f aca="false">IF($D51="","",IF($B51="","缺月份",IF($E51=0,"缺总工时",IF(ROUND($O51-$E51,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="28"/>
@@ -6480,6 +6706,10 @@
         <v/>
       </c>
       <c r="Q52" s="27"/>
+      <c r="R52" s="21" t="str">
+        <f aca="false">IF($D52="","",IF($B52="","缺月份",IF($E52=0,"缺总工时",IF(ROUND($O52-$E52,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="28"/>
@@ -6507,6 +6737,10 @@
         <v/>
       </c>
       <c r="Q53" s="27"/>
+      <c r="R53" s="21" t="str">
+        <f aca="false">IF($D53="","",IF($B53="","缺月份",IF($E53=0,"缺总工时",IF(ROUND($O53-$E53,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="28"/>
@@ -6534,6 +6768,10 @@
         <v/>
       </c>
       <c r="Q54" s="27"/>
+      <c r="R54" s="21" t="str">
+        <f aca="false">IF($D54="","",IF($B54="","缺月份",IF($E54=0,"缺总工时",IF(ROUND($O54-$E54,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="28"/>
@@ -6561,6 +6799,10 @@
         <v/>
       </c>
       <c r="Q55" s="27"/>
+      <c r="R55" s="21" t="str">
+        <f aca="false">IF($D55="","",IF($B55="","缺月份",IF($E55=0,"缺总工时",IF(ROUND($O55-$E55,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="28"/>
@@ -6588,6 +6830,10 @@
         <v/>
       </c>
       <c r="Q56" s="27"/>
+      <c r="R56" s="21" t="str">
+        <f aca="false">IF($D56="","",IF($B56="","缺月份",IF($E56=0,"缺总工时",IF(ROUND($O56-$E56,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="28"/>
@@ -6615,6 +6861,10 @@
         <v/>
       </c>
       <c r="Q57" s="27"/>
+      <c r="R57" s="21" t="str">
+        <f aca="false">IF($D57="","",IF($B57="","缺月份",IF($E57=0,"缺总工时",IF(ROUND($O57-$E57,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="28"/>
@@ -6642,6 +6892,10 @@
         <v/>
       </c>
       <c r="Q58" s="27"/>
+      <c r="R58" s="21" t="str">
+        <f aca="false">IF($D58="","",IF($B58="","缺月份",IF($E58=0,"缺总工时",IF(ROUND($O58-$E58,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="28"/>
@@ -6669,6 +6923,10 @@
         <v/>
       </c>
       <c r="Q59" s="27"/>
+      <c r="R59" s="21" t="str">
+        <f aca="false">IF($D59="","",IF($B59="","缺月份",IF($E59=0,"缺总工时",IF(ROUND($O59-$E59,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="28"/>
@@ -6696,6 +6954,10 @@
         <v/>
       </c>
       <c r="Q60" s="27"/>
+      <c r="R60" s="21" t="str">
+        <f aca="false">IF($D60="","",IF($B60="","缺月份",IF($E60=0,"缺总工时",IF(ROUND($O60-$E60,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="28"/>
@@ -6723,6 +6985,10 @@
         <v/>
       </c>
       <c r="Q61" s="27"/>
+      <c r="R61" s="21" t="str">
+        <f aca="false">IF($D61="","",IF($B61="","缺月份",IF($E61=0,"缺总工时",IF(ROUND($O61-$E61,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="28"/>
@@ -6750,6 +7016,10 @@
         <v/>
       </c>
       <c r="Q62" s="27"/>
+      <c r="R62" s="21" t="str">
+        <f aca="false">IF($D62="","",IF($B62="","缺月份",IF($E62=0,"缺总工时",IF(ROUND($O62-$E62,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="28"/>
@@ -6777,6 +7047,10 @@
         <v/>
       </c>
       <c r="Q63" s="27"/>
+      <c r="R63" s="21" t="str">
+        <f aca="false">IF($D63="","",IF($B63="","缺月份",IF($E63=0,"缺总工时",IF(ROUND($O63-$E63,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="28"/>
@@ -6804,6 +7078,10 @@
         <v/>
       </c>
       <c r="Q64" s="27"/>
+      <c r="R64" s="21" t="str">
+        <f aca="false">IF($D64="","",IF($B64="","缺月份",IF($E64=0,"缺总工时",IF(ROUND($O64-$E64,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="28"/>
@@ -6831,6 +7109,10 @@
         <v/>
       </c>
       <c r="Q65" s="27"/>
+      <c r="R65" s="21" t="str">
+        <f aca="false">IF($D65="","",IF($B65="","缺月份",IF($E65=0,"缺总工时",IF(ROUND($O65-$E65,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="28"/>
@@ -6858,6 +7140,10 @@
         <v/>
       </c>
       <c r="Q66" s="27"/>
+      <c r="R66" s="21" t="str">
+        <f aca="false">IF($D66="","",IF($B66="","缺月份",IF($E66=0,"缺总工时",IF(ROUND($O66-$E66,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="28"/>
@@ -6885,6 +7171,10 @@
         <v/>
       </c>
       <c r="Q67" s="27"/>
+      <c r="R67" s="21" t="str">
+        <f aca="false">IF($D67="","",IF($B67="","缺月份",IF($E67=0,"缺总工时",IF(ROUND($O67-$E67,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="28"/>
@@ -6912,6 +7202,10 @@
         <v/>
       </c>
       <c r="Q68" s="27"/>
+      <c r="R68" s="21" t="str">
+        <f aca="false">IF($D68="","",IF($B68="","缺月份",IF($E68=0,"缺总工时",IF(ROUND($O68-$E68,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="28"/>
@@ -6939,6 +7233,10 @@
         <v/>
       </c>
       <c r="Q69" s="27"/>
+      <c r="R69" s="21" t="str">
+        <f aca="false">IF($D69="","",IF($B69="","缺月份",IF($E69=0,"缺总工时",IF(ROUND($O69-$E69,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="28"/>
@@ -6966,6 +7264,10 @@
         <v/>
       </c>
       <c r="Q70" s="27"/>
+      <c r="R70" s="21" t="str">
+        <f aca="false">IF($D70="","",IF($B70="","缺月份",IF($E70=0,"缺总工时",IF(ROUND($O70-$E70,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="28"/>
@@ -6993,6 +7295,10 @@
         <v/>
       </c>
       <c r="Q71" s="27"/>
+      <c r="R71" s="21" t="str">
+        <f aca="false">IF($D71="","",IF($B71="","缺月份",IF($E71=0,"缺总工时",IF(ROUND($O71-$E71,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="28"/>
@@ -7020,6 +7326,10 @@
         <v/>
       </c>
       <c r="Q72" s="27"/>
+      <c r="R72" s="21" t="str">
+        <f aca="false">IF($D72="","",IF($B72="","缺月份",IF($E72=0,"缺总工时",IF(ROUND($O72-$E72,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="28"/>
@@ -7047,6 +7357,10 @@
         <v/>
       </c>
       <c r="Q73" s="27"/>
+      <c r="R73" s="21" t="str">
+        <f aca="false">IF($D73="","",IF($B73="","缺月份",IF($E73=0,"缺总工时",IF(ROUND($O73-$E73,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="28"/>
@@ -7074,6 +7388,10 @@
         <v/>
       </c>
       <c r="Q74" s="27"/>
+      <c r="R74" s="21" t="str">
+        <f aca="false">IF($D74="","",IF($B74="","缺月份",IF($E74=0,"缺总工时",IF(ROUND($O74-$E74,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="28"/>
@@ -7101,6 +7419,10 @@
         <v/>
       </c>
       <c r="Q75" s="27"/>
+      <c r="R75" s="21" t="str">
+        <f aca="false">IF($D75="","",IF($B75="","缺月份",IF($E75=0,"缺总工时",IF(ROUND($O75-$E75,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="28"/>
@@ -7128,6 +7450,10 @@
         <v/>
       </c>
       <c r="Q76" s="27"/>
+      <c r="R76" s="21" t="str">
+        <f aca="false">IF($D76="","",IF($B76="","缺月份",IF($E76=0,"缺总工时",IF(ROUND($O76-$E76,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="28"/>
@@ -7155,6 +7481,10 @@
         <v/>
       </c>
       <c r="Q77" s="27"/>
+      <c r="R77" s="21" t="str">
+        <f aca="false">IF($D77="","",IF($B77="","缺月份",IF($E77=0,"缺总工时",IF(ROUND($O77-$E77,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="28"/>
@@ -7182,6 +7512,10 @@
         <v/>
       </c>
       <c r="Q78" s="27"/>
+      <c r="R78" s="21" t="str">
+        <f aca="false">IF($D78="","",IF($B78="","缺月份",IF($E78=0,"缺总工时",IF(ROUND($O78-$E78,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="28"/>
@@ -7209,6 +7543,10 @@
         <v/>
       </c>
       <c r="Q79" s="27"/>
+      <c r="R79" s="21" t="str">
+        <f aca="false">IF($D79="","",IF($B79="","缺月份",IF($E79=0,"缺总工时",IF(ROUND($O79-$E79,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="28"/>
@@ -7236,6 +7574,10 @@
         <v/>
       </c>
       <c r="Q80" s="27"/>
+      <c r="R80" s="21" t="str">
+        <f aca="false">IF($D80="","",IF($B80="","缺月份",IF($E80=0,"缺总工时",IF(ROUND($O80-$E80,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="81" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="28"/>
@@ -7263,6 +7605,10 @@
         <v/>
       </c>
       <c r="Q81" s="27"/>
+      <c r="R81" s="21" t="str">
+        <f aca="false">IF($D81="","",IF($B81="","缺月份",IF($E81=0,"缺总工时",IF(ROUND($O81-$E81,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="82" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="28"/>
@@ -7290,6 +7636,10 @@
         <v/>
       </c>
       <c r="Q82" s="27"/>
+      <c r="R82" s="21" t="str">
+        <f aca="false">IF($D82="","",IF($B82="","缺月份",IF($E82=0,"缺总工时",IF(ROUND($O82-$E82,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="28"/>
@@ -7317,6 +7667,10 @@
         <v/>
       </c>
       <c r="Q83" s="27"/>
+      <c r="R83" s="21" t="str">
+        <f aca="false">IF($D83="","",IF($B83="","缺月份",IF($E83=0,"缺总工时",IF(ROUND($O83-$E83,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B84" s="28"/>
@@ -7344,6 +7698,10 @@
         <v/>
       </c>
       <c r="Q84" s="27"/>
+      <c r="R84" s="21" t="str">
+        <f aca="false">IF($D84="","",IF($B84="","缺月份",IF($E84=0,"缺总工时",IF(ROUND($O84-$E84,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="85" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="28"/>
@@ -7371,6 +7729,10 @@
         <v/>
       </c>
       <c r="Q85" s="27"/>
+      <c r="R85" s="21" t="str">
+        <f aca="false">IF($D85="","",IF($B85="","缺月份",IF($E85=0,"缺总工时",IF(ROUND($O85-$E85,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="86" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="28"/>
@@ -7398,6 +7760,10 @@
         <v/>
       </c>
       <c r="Q86" s="27"/>
+      <c r="R86" s="21" t="str">
+        <f aca="false">IF($D86="","",IF($B86="","缺月份",IF($E86=0,"缺总工时",IF(ROUND($O86-$E86,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B87" s="28"/>
@@ -7425,6 +7791,10 @@
         <v/>
       </c>
       <c r="Q87" s="27"/>
+      <c r="R87" s="21" t="str">
+        <f aca="false">IF($D87="","",IF($B87="","缺月份",IF($E87=0,"缺总工时",IF(ROUND($O87-$E87,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="88" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B88" s="28"/>
@@ -7452,6 +7822,10 @@
         <v/>
       </c>
       <c r="Q88" s="27"/>
+      <c r="R88" s="21" t="str">
+        <f aca="false">IF($D88="","",IF($B88="","缺月份",IF($E88=0,"缺总工时",IF(ROUND($O88-$E88,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="89" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B89" s="28"/>
@@ -7479,6 +7853,10 @@
         <v/>
       </c>
       <c r="Q89" s="27"/>
+      <c r="R89" s="21" t="str">
+        <f aca="false">IF($D89="","",IF($B89="","缺月份",IF($E89=0,"缺总工时",IF(ROUND($O89-$E89,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="90" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B90" s="28"/>
@@ -7506,6 +7884,10 @@
         <v/>
       </c>
       <c r="Q90" s="27"/>
+      <c r="R90" s="21" t="str">
+        <f aca="false">IF($D90="","",IF($B90="","缺月份",IF($E90=0,"缺总工时",IF(ROUND($O90-$E90,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="91" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B91" s="28"/>
@@ -7533,6 +7915,10 @@
         <v/>
       </c>
       <c r="Q91" s="27"/>
+      <c r="R91" s="21" t="str">
+        <f aca="false">IF($D91="","",IF($B91="","缺月份",IF($E91=0,"缺总工时",IF(ROUND($O91-$E91,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B92" s="28"/>
@@ -7560,6 +7946,10 @@
         <v/>
       </c>
       <c r="Q92" s="27"/>
+      <c r="R92" s="21" t="str">
+        <f aca="false">IF($D92="","",IF($B92="","缺月份",IF($E92=0,"缺总工时",IF(ROUND($O92-$E92,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="93" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B93" s="28"/>
@@ -7587,6 +7977,10 @@
         <v/>
       </c>
       <c r="Q93" s="27"/>
+      <c r="R93" s="21" t="str">
+        <f aca="false">IF($D93="","",IF($B93="","缺月份",IF($E93=0,"缺总工时",IF(ROUND($O93-$E93,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="94" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B94" s="28"/>
@@ -7614,6 +8008,10 @@
         <v/>
       </c>
       <c r="Q94" s="27"/>
+      <c r="R94" s="21" t="str">
+        <f aca="false">IF($D94="","",IF($B94="","缺月份",IF($E94=0,"缺总工时",IF(ROUND($O94-$E94,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="95" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B95" s="28"/>
@@ -7641,6 +8039,10 @@
         <v/>
       </c>
       <c r="Q95" s="27"/>
+      <c r="R95" s="21" t="str">
+        <f aca="false">IF($D95="","",IF($B95="","缺月份",IF($E95=0,"缺总工时",IF(ROUND($O95-$E95,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="96" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B96" s="28"/>
@@ -7668,6 +8070,10 @@
         <v/>
       </c>
       <c r="Q96" s="27"/>
+      <c r="R96" s="21" t="str">
+        <f aca="false">IF($D96="","",IF($B96="","缺月份",IF($E96=0,"缺总工时",IF(ROUND($O96-$E96,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="97" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B97" s="28"/>
@@ -7695,6 +8101,10 @@
         <v/>
       </c>
       <c r="Q97" s="27"/>
+      <c r="R97" s="21" t="str">
+        <f aca="false">IF($D97="","",IF($B97="","缺月份",IF($E97=0,"缺总工时",IF(ROUND($O97-$E97,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="98" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B98" s="28"/>
@@ -7722,6 +8132,10 @@
         <v/>
       </c>
       <c r="Q98" s="27"/>
+      <c r="R98" s="21" t="str">
+        <f aca="false">IF($D98="","",IF($B98="","缺月份",IF($E98=0,"缺总工时",IF(ROUND($O98-$E98,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="99" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B99" s="28"/>
@@ -7749,6 +8163,10 @@
         <v/>
       </c>
       <c r="Q99" s="27"/>
+      <c r="R99" s="21" t="str">
+        <f aca="false">IF($D99="","",IF($B99="","缺月份",IF($E99=0,"缺总工时",IF(ROUND($O99-$E99,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="100" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B100" s="28"/>
@@ -7776,6 +8194,10 @@
         <v/>
       </c>
       <c r="Q100" s="27"/>
+      <c r="R100" s="21" t="str">
+        <f aca="false">IF($D100="","",IF($B100="","缺月份",IF($E100=0,"缺总工时",IF(ROUND($O100-$E100,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="101" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B101" s="28"/>
@@ -7803,6 +8225,10 @@
         <v/>
       </c>
       <c r="Q101" s="27"/>
+      <c r="R101" s="21" t="str">
+        <f aca="false">IF($D101="","",IF($B101="","缺月份",IF($E101=0,"缺总工时",IF(ROUND($O101-$E101,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="102" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B102" s="28"/>
@@ -7830,6 +8256,10 @@
         <v/>
       </c>
       <c r="Q102" s="27"/>
+      <c r="R102" s="21" t="str">
+        <f aca="false">IF($D102="","",IF($B102="","缺月份",IF($E102=0,"缺总工时",IF(ROUND($O102-$E102,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="103" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B103" s="28"/>
@@ -7857,6 +8287,10 @@
         <v/>
       </c>
       <c r="Q103" s="27"/>
+      <c r="R103" s="21" t="str">
+        <f aca="false">IF($D103="","",IF($B103="","缺月份",IF($E103=0,"缺总工时",IF(ROUND($O103-$E103,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="104" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B104" s="28"/>
@@ -7884,6 +8318,10 @@
         <v/>
       </c>
       <c r="Q104" s="27"/>
+      <c r="R104" s="21" t="str">
+        <f aca="false">IF($D104="","",IF($B104="","缺月份",IF($E104=0,"缺总工时",IF(ROUND($O104-$E104,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="105" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B105" s="28"/>
@@ -7911,6 +8349,10 @@
         <v/>
       </c>
       <c r="Q105" s="27"/>
+      <c r="R105" s="21" t="str">
+        <f aca="false">IF($D105="","",IF($B105="","缺月份",IF($E105=0,"缺总工时",IF(ROUND($O105-$E105,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="106" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B106" s="28"/>
@@ -7938,6 +8380,10 @@
         <v/>
       </c>
       <c r="Q106" s="27"/>
+      <c r="R106" s="21" t="str">
+        <f aca="false">IF($D106="","",IF($B106="","缺月份",IF($E106=0,"缺总工时",IF(ROUND($O106-$E106,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="107" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B107" s="28"/>
@@ -7965,6 +8411,10 @@
         <v/>
       </c>
       <c r="Q107" s="27"/>
+      <c r="R107" s="21" t="str">
+        <f aca="false">IF($D107="","",IF($B107="","缺月份",IF($E107=0,"缺总工时",IF(ROUND($O107-$E107,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="108" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B108" s="28"/>
@@ -7992,6 +8442,10 @@
         <v/>
       </c>
       <c r="Q108" s="27"/>
+      <c r="R108" s="21" t="str">
+        <f aca="false">IF($D108="","",IF($B108="","缺月份",IF($E108=0,"缺总工时",IF(ROUND($O108-$E108,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="109" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B109" s="28"/>
@@ -8019,6 +8473,10 @@
         <v/>
       </c>
       <c r="Q109" s="27"/>
+      <c r="R109" s="21" t="str">
+        <f aca="false">IF($D109="","",IF($B109="","缺月份",IF($E109=0,"缺总工时",IF(ROUND($O109-$E109,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="110" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B110" s="28"/>
@@ -8046,6 +8504,10 @@
         <v/>
       </c>
       <c r="Q110" s="27"/>
+      <c r="R110" s="21" t="str">
+        <f aca="false">IF($D110="","",IF($B110="","缺月份",IF($E110=0,"缺总工时",IF(ROUND($O110-$E110,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="111" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B111" s="28"/>
@@ -8073,6 +8535,10 @@
         <v/>
       </c>
       <c r="Q111" s="27"/>
+      <c r="R111" s="21" t="str">
+        <f aca="false">IF($D111="","",IF($B111="","缺月份",IF($E111=0,"缺总工时",IF(ROUND($O111-$E111,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="112" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B112" s="28"/>
@@ -8100,6 +8566,10 @@
         <v/>
       </c>
       <c r="Q112" s="27"/>
+      <c r="R112" s="21" t="str">
+        <f aca="false">IF($D112="","",IF($B112="","缺月份",IF($E112=0,"缺总工时",IF(ROUND($O112-$E112,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="113" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B113" s="28"/>
@@ -8127,6 +8597,10 @@
         <v/>
       </c>
       <c r="Q113" s="27"/>
+      <c r="R113" s="21" t="str">
+        <f aca="false">IF($D113="","",IF($B113="","缺月份",IF($E113=0,"缺总工时",IF(ROUND($O113-$E113,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="114" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B114" s="28"/>
@@ -8154,6 +8628,10 @@
         <v/>
       </c>
       <c r="Q114" s="27"/>
+      <c r="R114" s="21" t="str">
+        <f aca="false">IF($D114="","",IF($B114="","缺月份",IF($E114=0,"缺总工时",IF(ROUND($O114-$E114,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="115" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B115" s="28"/>
@@ -8181,6 +8659,10 @@
         <v/>
       </c>
       <c r="Q115" s="27"/>
+      <c r="R115" s="21" t="str">
+        <f aca="false">IF($D115="","",IF($B115="","缺月份",IF($E115=0,"缺总工时",IF(ROUND($O115-$E115,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="116" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B116" s="28"/>
@@ -8208,6 +8690,10 @@
         <v/>
       </c>
       <c r="Q116" s="27"/>
+      <c r="R116" s="21" t="str">
+        <f aca="false">IF($D116="","",IF($B116="","缺月份",IF($E116=0,"缺总工时",IF(ROUND($O116-$E116,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="117" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B117" s="28"/>
@@ -8235,6 +8721,10 @@
         <v/>
       </c>
       <c r="Q117" s="27"/>
+      <c r="R117" s="21" t="str">
+        <f aca="false">IF($D117="","",IF($B117="","缺月份",IF($E117=0,"缺总工时",IF(ROUND($O117-$E117,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="118" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B118" s="28"/>
@@ -8262,6 +8752,10 @@
         <v/>
       </c>
       <c r="Q118" s="27"/>
+      <c r="R118" s="21" t="str">
+        <f aca="false">IF($D118="","",IF($B118="","缺月份",IF($E118=0,"缺总工时",IF(ROUND($O118-$E118,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="119" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B119" s="28"/>
@@ -8289,6 +8783,10 @@
         <v/>
       </c>
       <c r="Q119" s="27"/>
+      <c r="R119" s="21" t="str">
+        <f aca="false">IF($D119="","",IF($B119="","缺月份",IF($E119=0,"缺总工时",IF(ROUND($O119-$E119,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="120" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B120" s="28"/>
@@ -8316,6 +8814,10 @@
         <v/>
       </c>
       <c r="Q120" s="27"/>
+      <c r="R120" s="21" t="str">
+        <f aca="false">IF($D120="","",IF($B120="","缺月份",IF($E120=0,"缺总工时",IF(ROUND($O120-$E120,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="121" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B121" s="28"/>
@@ -8343,6 +8845,10 @@
         <v/>
       </c>
       <c r="Q121" s="27"/>
+      <c r="R121" s="21" t="str">
+        <f aca="false">IF($D121="","",IF($B121="","缺月份",IF($E121=0,"缺总工时",IF(ROUND($O121-$E121,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="122" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B122" s="28"/>
@@ -8370,6 +8876,10 @@
         <v/>
       </c>
       <c r="Q122" s="27"/>
+      <c r="R122" s="21" t="str">
+        <f aca="false">IF($D122="","",IF($B122="","缺月份",IF($E122=0,"缺总工时",IF(ROUND($O122-$E122,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="123" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B123" s="28"/>
@@ -8397,6 +8907,10 @@
         <v/>
       </c>
       <c r="Q123" s="27"/>
+      <c r="R123" s="21" t="str">
+        <f aca="false">IF($D123="","",IF($B123="","缺月份",IF($E123=0,"缺总工时",IF(ROUND($O123-$E123,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="124" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B124" s="28"/>
@@ -8424,6 +8938,10 @@
         <v/>
       </c>
       <c r="Q124" s="27"/>
+      <c r="R124" s="21" t="str">
+        <f aca="false">IF($D124="","",IF($B124="","缺月份",IF($E124=0,"缺总工时",IF(ROUND($O124-$E124,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="125" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B125" s="28"/>
@@ -8451,6 +8969,10 @@
         <v/>
       </c>
       <c r="Q125" s="27"/>
+      <c r="R125" s="21" t="str">
+        <f aca="false">IF($D125="","",IF($B125="","缺月份",IF($E125=0,"缺总工时",IF(ROUND($O125-$E125,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="126" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B126" s="28"/>
@@ -8478,10 +9000,14 @@
         <v/>
       </c>
       <c r="Q126" s="27"/>
+      <c r="R126" s="21" t="str">
+        <f aca="false">IF($D126="","",IF($B126="","缺月份",IF($E126=0,"缺总工时",IF(ROUND($O126-$E126,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="B2:Q2"/>
+  <mergeCells count="11">
+    <mergeCell ref="B2:R2"/>
     <mergeCell ref="B4:B6"/>
     <mergeCell ref="C4:C6"/>
     <mergeCell ref="D4:D6"/>
@@ -8489,6 +9015,7 @@
     <mergeCell ref="F4:F6"/>
     <mergeCell ref="G4:O4"/>
     <mergeCell ref="Q4:Q6"/>
+    <mergeCell ref="R4:R6"/>
     <mergeCell ref="O5:O6"/>
     <mergeCell ref="P5:P6"/>
   </mergeCells>
@@ -8513,7 +9040,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:R150"/>
+  <dimension ref="B2:S150"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -8523,11 +9050,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="6" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="11"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -8545,36 +9073,37 @@
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q3" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="R3" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I4" s="15"/>
       <c r="J4" s="15"/>
@@ -8585,10 +9114,13 @@
       <c r="O4" s="15"/>
       <c r="P4" s="15"/>
       <c r="Q4" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="R4" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="S4" s="14" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8631,12 +9163,13 @@
         <v>RD08</v>
       </c>
       <c r="P5" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q5" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="R5" s="14"/>
+      <c r="S5" s="14"/>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="14"/>
@@ -8680,6 +9213,7 @@
       <c r="P6" s="14"/>
       <c r="Q6" s="14"/>
       <c r="R6" s="14"/>
+      <c r="S6" s="14"/>
     </row>
     <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="28" t="n">
@@ -8689,10 +9223,10 @@
         <v>1</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F7" s="18" t="n">
         <v>180</v>
@@ -8726,7 +9260,11 @@
         <v>0.8</v>
       </c>
       <c r="R7" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="S7" s="21" t="str">
+        <f aca="false">IF($D7="","",IF($B7="","缺月份",IF($F7=0,"缺总工时",IF(ROUND($P7-$F7,2)&gt;0,"工时超出","√"))))</f>
+        <v>√</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8737,10 +9275,10 @@
         <v>2</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F8" s="18" t="n">
         <v>180</v>
@@ -8772,7 +9310,11 @@
         <v>0.6</v>
       </c>
       <c r="R8" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="S8" s="21" t="str">
+        <f aca="false">IF($D8="","",IF($B8="","缺月份",IF($F8=0,"缺总工时",IF(ROUND($P8-$F8,2)&gt;0,"工时超出","√"))))</f>
+        <v>√</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8783,10 +9325,10 @@
         <v>3</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F9" s="18" t="n">
         <v>180</v>
@@ -8820,7 +9362,11 @@
         <v>0.8</v>
       </c>
       <c r="R9" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="S9" s="21" t="str">
+        <f aca="false">IF($D9="","",IF($B9="","缺月份",IF($F9=0,"缺总工时",IF(ROUND($P9-$F9,2)&gt;0,"工时超出","√"))))</f>
+        <v>√</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8831,10 +9377,10 @@
         <v>4</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F10" s="18" t="n">
         <v>180</v>
@@ -8866,7 +9412,11 @@
         <v>0.6</v>
       </c>
       <c r="R10" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="S10" s="21" t="str">
+        <f aca="false">IF($D10="","",IF($B10="","缺月份",IF($F10=0,"缺总工时",IF(ROUND($P10-$F10,2)&gt;0,"工时超出","√"))))</f>
+        <v>√</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8877,10 +9427,10 @@
         <v>5</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F11" s="18" t="n">
         <v>180</v>
@@ -8910,7 +9460,11 @@
         <v>0.4</v>
       </c>
       <c r="R11" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="S11" s="21" t="str">
+        <f aca="false">IF($D11="","",IF($B11="","缺月份",IF($F11=0,"缺总工时",IF(ROUND($P11-$F11,2)&gt;0,"工时超出","√"))))</f>
+        <v>√</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8921,10 +9475,10 @@
         <v>6</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F12" s="18" t="n">
         <v>180</v>
@@ -8952,7 +9506,11 @@
         <v>0.2</v>
       </c>
       <c r="R12" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="S12" s="21" t="str">
+        <f aca="false">IF($D12="","",IF($B12="","缺月份",IF($F12=0,"缺总工时",IF(ROUND($P12-$F12,2)&gt;0,"工时超出","√"))))</f>
+        <v>√</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8963,10 +9521,10 @@
         <v>7</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F13" s="18" t="n">
         <v>180</v>
@@ -8994,7 +9552,11 @@
         <v>0.2</v>
       </c>
       <c r="R13" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="S13" s="21" t="str">
+        <f aca="false">IF($D13="","",IF($B13="","缺月份",IF($F13=0,"缺总工时",IF(ROUND($P13-$F13,2)&gt;0,"工时超出","√"))))</f>
+        <v>√</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9005,10 +9567,10 @@
         <v>8</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F14" s="18" t="n">
         <v>180</v>
@@ -9034,7 +9596,11 @@
         <v>0</v>
       </c>
       <c r="R14" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="S14" s="21" t="str">
+        <f aca="false">IF($D14="","",IF($B14="","缺月份",IF($F14=0,"缺总工时",IF(ROUND($P14-$F14,2)&gt;0,"工时超出","√"))))</f>
+        <v>√</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9045,10 +9611,10 @@
         <v>9</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F15" s="18" t="n">
         <v>180</v>
@@ -9076,7 +9642,11 @@
         <v>0.2</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="S15" s="21" t="str">
+        <f aca="false">IF($D15="","",IF($B15="","缺月份",IF($F15=0,"缺总工时",IF(ROUND($P15-$F15,2)&gt;0,"工时超出","√"))))</f>
+        <v>√</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9087,10 +9657,10 @@
         <v>10</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F16" s="18" t="n">
         <v>180</v>
@@ -9118,7 +9688,11 @@
         <v>0.2</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="S16" s="21" t="str">
+        <f aca="false">IF($D16="","",IF($B16="","缺月份",IF($F16=0,"缺总工时",IF(ROUND($P16-$F16,2)&gt;0,"工时超出","√"))))</f>
+        <v>√</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9129,10 +9703,10 @@
         <v>11</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F17" s="18" t="n">
         <v>180</v>
@@ -9168,7 +9742,11 @@
         <v>1</v>
       </c>
       <c r="R17" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="S17" s="21" t="str">
+        <f aca="false">IF($D17="","",IF($B17="","缺月份",IF($F17=0,"缺总工时",IF(ROUND($P17-$F17,2)&gt;0,"工时超出","√"))))</f>
+        <v>√</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9198,6 +9776,10 @@
         <v/>
       </c>
       <c r="R18" s="27"/>
+      <c r="S18" s="21" t="str">
+        <f aca="false">IF($D18="","",IF($B18="","缺月份",IF($F18=0,"缺总工时",IF(ROUND($P18-$F18,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="28"/>
@@ -9226,6 +9808,10 @@
         <v/>
       </c>
       <c r="R19" s="27"/>
+      <c r="S19" s="21" t="str">
+        <f aca="false">IF($D19="","",IF($B19="","缺月份",IF($F19=0,"缺总工时",IF(ROUND($P19-$F19,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="28"/>
@@ -9254,6 +9840,10 @@
         <v/>
       </c>
       <c r="R20" s="27"/>
+      <c r="S20" s="21" t="str">
+        <f aca="false">IF($D20="","",IF($B20="","缺月份",IF($F20=0,"缺总工时",IF(ROUND($P20-$F20,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="28"/>
@@ -9282,6 +9872,10 @@
         <v/>
       </c>
       <c r="R21" s="27"/>
+      <c r="S21" s="21" t="str">
+        <f aca="false">IF($D21="","",IF($B21="","缺月份",IF($F21=0,"缺总工时",IF(ROUND($P21-$F21,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="28"/>
@@ -9310,6 +9904,10 @@
         <v/>
       </c>
       <c r="R22" s="27"/>
+      <c r="S22" s="21" t="str">
+        <f aca="false">IF($D22="","",IF($B22="","缺月份",IF($F22=0,"缺总工时",IF(ROUND($P22-$F22,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="28"/>
@@ -9338,6 +9936,10 @@
         <v/>
       </c>
       <c r="R23" s="27"/>
+      <c r="S23" s="21" t="str">
+        <f aca="false">IF($D23="","",IF($B23="","缺月份",IF($F23=0,"缺总工时",IF(ROUND($P23-$F23,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="28"/>
@@ -9366,6 +9968,10 @@
         <v/>
       </c>
       <c r="R24" s="27"/>
+      <c r="S24" s="21" t="str">
+        <f aca="false">IF($D24="","",IF($B24="","缺月份",IF($F24=0,"缺总工时",IF(ROUND($P24-$F24,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="28"/>
@@ -9394,6 +10000,10 @@
         <v/>
       </c>
       <c r="R25" s="27"/>
+      <c r="S25" s="21" t="str">
+        <f aca="false">IF($D25="","",IF($B25="","缺月份",IF($F25=0,"缺总工时",IF(ROUND($P25-$F25,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="28"/>
@@ -9422,6 +10032,10 @@
         <v/>
       </c>
       <c r="R26" s="27"/>
+      <c r="S26" s="21" t="str">
+        <f aca="false">IF($D26="","",IF($B26="","缺月份",IF($F26=0,"缺总工时",IF(ROUND($P26-$F26,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="28"/>
@@ -9450,6 +10064,10 @@
         <v/>
       </c>
       <c r="R27" s="27"/>
+      <c r="S27" s="21" t="str">
+        <f aca="false">IF($D27="","",IF($B27="","缺月份",IF($F27=0,"缺总工时",IF(ROUND($P27-$F27,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="28"/>
@@ -9478,6 +10096,10 @@
         <v/>
       </c>
       <c r="R28" s="27"/>
+      <c r="S28" s="21" t="str">
+        <f aca="false">IF($D28="","",IF($B28="","缺月份",IF($F28=0,"缺总工时",IF(ROUND($P28-$F28,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="28"/>
@@ -9506,6 +10128,10 @@
         <v/>
       </c>
       <c r="R29" s="27"/>
+      <c r="S29" s="21" t="str">
+        <f aca="false">IF($D29="","",IF($B29="","缺月份",IF($F29=0,"缺总工时",IF(ROUND($P29-$F29,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="28"/>
@@ -9534,6 +10160,10 @@
         <v/>
       </c>
       <c r="R30" s="27"/>
+      <c r="S30" s="21" t="str">
+        <f aca="false">IF($D30="","",IF($B30="","缺月份",IF($F30=0,"缺总工时",IF(ROUND($P30-$F30,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="28"/>
@@ -9562,6 +10192,10 @@
         <v/>
       </c>
       <c r="R31" s="27"/>
+      <c r="S31" s="21" t="str">
+        <f aca="false">IF($D31="","",IF($B31="","缺月份",IF($F31=0,"缺总工时",IF(ROUND($P31-$F31,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="28"/>
@@ -9590,6 +10224,10 @@
         <v/>
       </c>
       <c r="R32" s="27"/>
+      <c r="S32" s="21" t="str">
+        <f aca="false">IF($D32="","",IF($B32="","缺月份",IF($F32=0,"缺总工时",IF(ROUND($P32-$F32,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="28"/>
@@ -9618,6 +10256,10 @@
         <v/>
       </c>
       <c r="R33" s="27"/>
+      <c r="S33" s="21" t="str">
+        <f aca="false">IF($D33="","",IF($B33="","缺月份",IF($F33=0,"缺总工时",IF(ROUND($P33-$F33,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="28"/>
@@ -9646,6 +10288,10 @@
         <v/>
       </c>
       <c r="R34" s="27"/>
+      <c r="S34" s="21" t="str">
+        <f aca="false">IF($D34="","",IF($B34="","缺月份",IF($F34=0,"缺总工时",IF(ROUND($P34-$F34,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="28"/>
@@ -9674,6 +10320,10 @@
         <v/>
       </c>
       <c r="R35" s="27"/>
+      <c r="S35" s="21" t="str">
+        <f aca="false">IF($D35="","",IF($B35="","缺月份",IF($F35=0,"缺总工时",IF(ROUND($P35-$F35,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="28"/>
@@ -9702,6 +10352,10 @@
         <v/>
       </c>
       <c r="R36" s="27"/>
+      <c r="S36" s="21" t="str">
+        <f aca="false">IF($D36="","",IF($B36="","缺月份",IF($F36=0,"缺总工时",IF(ROUND($P36-$F36,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="28"/>
@@ -9730,6 +10384,10 @@
         <v/>
       </c>
       <c r="R37" s="27"/>
+      <c r="S37" s="21" t="str">
+        <f aca="false">IF($D37="","",IF($B37="","缺月份",IF($F37=0,"缺总工时",IF(ROUND($P37-$F37,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="28"/>
@@ -9758,6 +10416,10 @@
         <v/>
       </c>
       <c r="R38" s="27"/>
+      <c r="S38" s="21" t="str">
+        <f aca="false">IF($D38="","",IF($B38="","缺月份",IF($F38=0,"缺总工时",IF(ROUND($P38-$F38,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="28"/>
@@ -9786,6 +10448,10 @@
         <v/>
       </c>
       <c r="R39" s="27"/>
+      <c r="S39" s="21" t="str">
+        <f aca="false">IF($D39="","",IF($B39="","缺月份",IF($F39=0,"缺总工时",IF(ROUND($P39-$F39,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="28"/>
@@ -9814,6 +10480,10 @@
         <v/>
       </c>
       <c r="R40" s="27"/>
+      <c r="S40" s="21" t="str">
+        <f aca="false">IF($D40="","",IF($B40="","缺月份",IF($F40=0,"缺总工时",IF(ROUND($P40-$F40,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="28"/>
@@ -9842,6 +10512,10 @@
         <v/>
       </c>
       <c r="R41" s="27"/>
+      <c r="S41" s="21" t="str">
+        <f aca="false">IF($D41="","",IF($B41="","缺月份",IF($F41=0,"缺总工时",IF(ROUND($P41-$F41,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="28"/>
@@ -9870,6 +10544,10 @@
         <v/>
       </c>
       <c r="R42" s="27"/>
+      <c r="S42" s="21" t="str">
+        <f aca="false">IF($D42="","",IF($B42="","缺月份",IF($F42=0,"缺总工时",IF(ROUND($P42-$F42,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="28"/>
@@ -9898,6 +10576,10 @@
         <v/>
       </c>
       <c r="R43" s="27"/>
+      <c r="S43" s="21" t="str">
+        <f aca="false">IF($D43="","",IF($B43="","缺月份",IF($F43=0,"缺总工时",IF(ROUND($P43-$F43,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="28"/>
@@ -9926,6 +10608,10 @@
         <v/>
       </c>
       <c r="R44" s="27"/>
+      <c r="S44" s="21" t="str">
+        <f aca="false">IF($D44="","",IF($B44="","缺月份",IF($F44=0,"缺总工时",IF(ROUND($P44-$F44,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="28"/>
@@ -9954,6 +10640,10 @@
         <v/>
       </c>
       <c r="R45" s="27"/>
+      <c r="S45" s="21" t="str">
+        <f aca="false">IF($D45="","",IF($B45="","缺月份",IF($F45=0,"缺总工时",IF(ROUND($P45-$F45,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="28"/>
@@ -9982,6 +10672,10 @@
         <v/>
       </c>
       <c r="R46" s="27"/>
+      <c r="S46" s="21" t="str">
+        <f aca="false">IF($D46="","",IF($B46="","缺月份",IF($F46=0,"缺总工时",IF(ROUND($P46-$F46,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="28"/>
@@ -10010,6 +10704,10 @@
         <v/>
       </c>
       <c r="R47" s="27"/>
+      <c r="S47" s="21" t="str">
+        <f aca="false">IF($D47="","",IF($B47="","缺月份",IF($F47=0,"缺总工时",IF(ROUND($P47-$F47,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="28"/>
@@ -10038,6 +10736,10 @@
         <v/>
       </c>
       <c r="R48" s="27"/>
+      <c r="S48" s="21" t="str">
+        <f aca="false">IF($D48="","",IF($B48="","缺月份",IF($F48=0,"缺总工时",IF(ROUND($P48-$F48,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="28"/>
@@ -10066,6 +10768,10 @@
         <v/>
       </c>
       <c r="R49" s="27"/>
+      <c r="S49" s="21" t="str">
+        <f aca="false">IF($D49="","",IF($B49="","缺月份",IF($F49=0,"缺总工时",IF(ROUND($P49-$F49,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="28"/>
@@ -10094,6 +10800,10 @@
         <v/>
       </c>
       <c r="R50" s="27"/>
+      <c r="S50" s="21" t="str">
+        <f aca="false">IF($D50="","",IF($B50="","缺月份",IF($F50=0,"缺总工时",IF(ROUND($P50-$F50,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="28"/>
@@ -10122,6 +10832,10 @@
         <v/>
       </c>
       <c r="R51" s="27"/>
+      <c r="S51" s="21" t="str">
+        <f aca="false">IF($D51="","",IF($B51="","缺月份",IF($F51=0,"缺总工时",IF(ROUND($P51-$F51,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="28"/>
@@ -10150,6 +10864,10 @@
         <v/>
       </c>
       <c r="R52" s="27"/>
+      <c r="S52" s="21" t="str">
+        <f aca="false">IF($D52="","",IF($B52="","缺月份",IF($F52=0,"缺总工时",IF(ROUND($P52-$F52,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="28"/>
@@ -10178,6 +10896,10 @@
         <v/>
       </c>
       <c r="R53" s="27"/>
+      <c r="S53" s="21" t="str">
+        <f aca="false">IF($D53="","",IF($B53="","缺月份",IF($F53=0,"缺总工时",IF(ROUND($P53-$F53,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="28"/>
@@ -10206,6 +10928,10 @@
         <v/>
       </c>
       <c r="R54" s="27"/>
+      <c r="S54" s="21" t="str">
+        <f aca="false">IF($D54="","",IF($B54="","缺月份",IF($F54=0,"缺总工时",IF(ROUND($P54-$F54,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="28"/>
@@ -10234,6 +10960,10 @@
         <v/>
       </c>
       <c r="R55" s="27"/>
+      <c r="S55" s="21" t="str">
+        <f aca="false">IF($D55="","",IF($B55="","缺月份",IF($F55=0,"缺总工时",IF(ROUND($P55-$F55,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="28"/>
@@ -10262,6 +10992,10 @@
         <v/>
       </c>
       <c r="R56" s="27"/>
+      <c r="S56" s="21" t="str">
+        <f aca="false">IF($D56="","",IF($B56="","缺月份",IF($F56=0,"缺总工时",IF(ROUND($P56-$F56,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="28"/>
@@ -10290,6 +11024,10 @@
         <v/>
       </c>
       <c r="R57" s="27"/>
+      <c r="S57" s="21" t="str">
+        <f aca="false">IF($D57="","",IF($B57="","缺月份",IF($F57=0,"缺总工时",IF(ROUND($P57-$F57,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="28"/>
@@ -10318,6 +11056,10 @@
         <v/>
       </c>
       <c r="R58" s="27"/>
+      <c r="S58" s="21" t="str">
+        <f aca="false">IF($D58="","",IF($B58="","缺月份",IF($F58=0,"缺总工时",IF(ROUND($P58-$F58,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="28"/>
@@ -10346,6 +11088,10 @@
         <v/>
       </c>
       <c r="R59" s="27"/>
+      <c r="S59" s="21" t="str">
+        <f aca="false">IF($D59="","",IF($B59="","缺月份",IF($F59=0,"缺总工时",IF(ROUND($P59-$F59,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="28"/>
@@ -10374,6 +11120,10 @@
         <v/>
       </c>
       <c r="R60" s="27"/>
+      <c r="S60" s="21" t="str">
+        <f aca="false">IF($D60="","",IF($B60="","缺月份",IF($F60=0,"缺总工时",IF(ROUND($P60-$F60,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="28"/>
@@ -10402,6 +11152,10 @@
         <v/>
       </c>
       <c r="R61" s="27"/>
+      <c r="S61" s="21" t="str">
+        <f aca="false">IF($D61="","",IF($B61="","缺月份",IF($F61=0,"缺总工时",IF(ROUND($P61-$F61,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="28"/>
@@ -10430,6 +11184,10 @@
         <v/>
       </c>
       <c r="R62" s="27"/>
+      <c r="S62" s="21" t="str">
+        <f aca="false">IF($D62="","",IF($B62="","缺月份",IF($F62=0,"缺总工时",IF(ROUND($P62-$F62,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="28"/>
@@ -10458,6 +11216,10 @@
         <v/>
       </c>
       <c r="R63" s="27"/>
+      <c r="S63" s="21" t="str">
+        <f aca="false">IF($D63="","",IF($B63="","缺月份",IF($F63=0,"缺总工时",IF(ROUND($P63-$F63,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="28"/>
@@ -10486,6 +11248,10 @@
         <v/>
       </c>
       <c r="R64" s="27"/>
+      <c r="S64" s="21" t="str">
+        <f aca="false">IF($D64="","",IF($B64="","缺月份",IF($F64=0,"缺总工时",IF(ROUND($P64-$F64,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="28"/>
@@ -10514,6 +11280,10 @@
         <v/>
       </c>
       <c r="R65" s="27"/>
+      <c r="S65" s="21" t="str">
+        <f aca="false">IF($D65="","",IF($B65="","缺月份",IF($F65=0,"缺总工时",IF(ROUND($P65-$F65,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="28"/>
@@ -10542,6 +11312,10 @@
         <v/>
       </c>
       <c r="R66" s="27"/>
+      <c r="S66" s="21" t="str">
+        <f aca="false">IF($D66="","",IF($B66="","缺月份",IF($F66=0,"缺总工时",IF(ROUND($P66-$F66,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="28"/>
@@ -10570,6 +11344,10 @@
         <v/>
       </c>
       <c r="R67" s="27"/>
+      <c r="S67" s="21" t="str">
+        <f aca="false">IF($D67="","",IF($B67="","缺月份",IF($F67=0,"缺总工时",IF(ROUND($P67-$F67,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="28"/>
@@ -10598,6 +11376,10 @@
         <v/>
       </c>
       <c r="R68" s="27"/>
+      <c r="S68" s="21" t="str">
+        <f aca="false">IF($D68="","",IF($B68="","缺月份",IF($F68=0,"缺总工时",IF(ROUND($P68-$F68,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="28"/>
@@ -10626,6 +11408,10 @@
         <v/>
       </c>
       <c r="R69" s="27"/>
+      <c r="S69" s="21" t="str">
+        <f aca="false">IF($D69="","",IF($B69="","缺月份",IF($F69=0,"缺总工时",IF(ROUND($P69-$F69,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="28"/>
@@ -10654,6 +11440,10 @@
         <v/>
       </c>
       <c r="R70" s="27"/>
+      <c r="S70" s="21" t="str">
+        <f aca="false">IF($D70="","",IF($B70="","缺月份",IF($F70=0,"缺总工时",IF(ROUND($P70-$F70,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="28"/>
@@ -10682,6 +11472,10 @@
         <v/>
       </c>
       <c r="R71" s="27"/>
+      <c r="S71" s="21" t="str">
+        <f aca="false">IF($D71="","",IF($B71="","缺月份",IF($F71=0,"缺总工时",IF(ROUND($P71-$F71,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="28"/>
@@ -10710,6 +11504,10 @@
         <v/>
       </c>
       <c r="R72" s="27"/>
+      <c r="S72" s="21" t="str">
+        <f aca="false">IF($D72="","",IF($B72="","缺月份",IF($F72=0,"缺总工时",IF(ROUND($P72-$F72,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="28"/>
@@ -10738,6 +11536,10 @@
         <v/>
       </c>
       <c r="R73" s="27"/>
+      <c r="S73" s="21" t="str">
+        <f aca="false">IF($D73="","",IF($B73="","缺月份",IF($F73=0,"缺总工时",IF(ROUND($P73-$F73,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="28"/>
@@ -10766,6 +11568,10 @@
         <v/>
       </c>
       <c r="R74" s="27"/>
+      <c r="S74" s="21" t="str">
+        <f aca="false">IF($D74="","",IF($B74="","缺月份",IF($F74=0,"缺总工时",IF(ROUND($P74-$F74,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="28"/>
@@ -10794,6 +11600,10 @@
         <v/>
       </c>
       <c r="R75" s="27"/>
+      <c r="S75" s="21" t="str">
+        <f aca="false">IF($D75="","",IF($B75="","缺月份",IF($F75=0,"缺总工时",IF(ROUND($P75-$F75,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="28"/>
@@ -10822,6 +11632,10 @@
         <v/>
       </c>
       <c r="R76" s="27"/>
+      <c r="S76" s="21" t="str">
+        <f aca="false">IF($D76="","",IF($B76="","缺月份",IF($F76=0,"缺总工时",IF(ROUND($P76-$F76,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="28"/>
@@ -10850,6 +11664,10 @@
         <v/>
       </c>
       <c r="R77" s="27"/>
+      <c r="S77" s="21" t="str">
+        <f aca="false">IF($D77="","",IF($B77="","缺月份",IF($F77=0,"缺总工时",IF(ROUND($P77-$F77,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="28"/>
@@ -10878,6 +11696,10 @@
         <v/>
       </c>
       <c r="R78" s="27"/>
+      <c r="S78" s="21" t="str">
+        <f aca="false">IF($D78="","",IF($B78="","缺月份",IF($F78=0,"缺总工时",IF(ROUND($P78-$F78,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="28"/>
@@ -10906,6 +11728,10 @@
         <v/>
       </c>
       <c r="R79" s="27"/>
+      <c r="S79" s="21" t="str">
+        <f aca="false">IF($D79="","",IF($B79="","缺月份",IF($F79=0,"缺总工时",IF(ROUND($P79-$F79,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="28"/>
@@ -10934,6 +11760,10 @@
         <v/>
       </c>
       <c r="R80" s="27"/>
+      <c r="S80" s="21" t="str">
+        <f aca="false">IF($D80="","",IF($B80="","缺月份",IF($F80=0,"缺总工时",IF(ROUND($P80-$F80,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="81" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="28"/>
@@ -10962,6 +11792,10 @@
         <v/>
       </c>
       <c r="R81" s="27"/>
+      <c r="S81" s="21" t="str">
+        <f aca="false">IF($D81="","",IF($B81="","缺月份",IF($F81=0,"缺总工时",IF(ROUND($P81-$F81,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="82" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="28"/>
@@ -10990,6 +11824,10 @@
         <v/>
       </c>
       <c r="R82" s="27"/>
+      <c r="S82" s="21" t="str">
+        <f aca="false">IF($D82="","",IF($B82="","缺月份",IF($F82=0,"缺总工时",IF(ROUND($P82-$F82,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="28"/>
@@ -11018,6 +11856,10 @@
         <v/>
       </c>
       <c r="R83" s="27"/>
+      <c r="S83" s="21" t="str">
+        <f aca="false">IF($D83="","",IF($B83="","缺月份",IF($F83=0,"缺总工时",IF(ROUND($P83-$F83,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B84" s="28"/>
@@ -11046,6 +11888,10 @@
         <v/>
       </c>
       <c r="R84" s="27"/>
+      <c r="S84" s="21" t="str">
+        <f aca="false">IF($D84="","",IF($B84="","缺月份",IF($F84=0,"缺总工时",IF(ROUND($P84-$F84,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="85" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="28"/>
@@ -11074,6 +11920,10 @@
         <v/>
       </c>
       <c r="R85" s="27"/>
+      <c r="S85" s="21" t="str">
+        <f aca="false">IF($D85="","",IF($B85="","缺月份",IF($F85=0,"缺总工时",IF(ROUND($P85-$F85,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="86" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="28"/>
@@ -11102,6 +11952,10 @@
         <v/>
       </c>
       <c r="R86" s="27"/>
+      <c r="S86" s="21" t="str">
+        <f aca="false">IF($D86="","",IF($B86="","缺月份",IF($F86=0,"缺总工时",IF(ROUND($P86-$F86,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B87" s="28"/>
@@ -11130,6 +11984,10 @@
         <v/>
       </c>
       <c r="R87" s="27"/>
+      <c r="S87" s="21" t="str">
+        <f aca="false">IF($D87="","",IF($B87="","缺月份",IF($F87=0,"缺总工时",IF(ROUND($P87-$F87,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="88" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B88" s="28"/>
@@ -11158,6 +12016,10 @@
         <v/>
       </c>
       <c r="R88" s="27"/>
+      <c r="S88" s="21" t="str">
+        <f aca="false">IF($D88="","",IF($B88="","缺月份",IF($F88=0,"缺总工时",IF(ROUND($P88-$F88,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="89" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B89" s="28"/>
@@ -11186,6 +12048,10 @@
         <v/>
       </c>
       <c r="R89" s="27"/>
+      <c r="S89" s="21" t="str">
+        <f aca="false">IF($D89="","",IF($B89="","缺月份",IF($F89=0,"缺总工时",IF(ROUND($P89-$F89,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="90" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B90" s="28"/>
@@ -11214,6 +12080,10 @@
         <v/>
       </c>
       <c r="R90" s="27"/>
+      <c r="S90" s="21" t="str">
+        <f aca="false">IF($D90="","",IF($B90="","缺月份",IF($F90=0,"缺总工时",IF(ROUND($P90-$F90,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="91" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B91" s="28"/>
@@ -11242,6 +12112,10 @@
         <v/>
       </c>
       <c r="R91" s="27"/>
+      <c r="S91" s="21" t="str">
+        <f aca="false">IF($D91="","",IF($B91="","缺月份",IF($F91=0,"缺总工时",IF(ROUND($P91-$F91,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B92" s="28"/>
@@ -11270,6 +12144,10 @@
         <v/>
       </c>
       <c r="R92" s="27"/>
+      <c r="S92" s="21" t="str">
+        <f aca="false">IF($D92="","",IF($B92="","缺月份",IF($F92=0,"缺总工时",IF(ROUND($P92-$F92,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="93" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B93" s="28"/>
@@ -11298,6 +12176,10 @@
         <v/>
       </c>
       <c r="R93" s="27"/>
+      <c r="S93" s="21" t="str">
+        <f aca="false">IF($D93="","",IF($B93="","缺月份",IF($F93=0,"缺总工时",IF(ROUND($P93-$F93,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="94" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B94" s="28"/>
@@ -11326,6 +12208,10 @@
         <v/>
       </c>
       <c r="R94" s="27"/>
+      <c r="S94" s="21" t="str">
+        <f aca="false">IF($D94="","",IF($B94="","缺月份",IF($F94=0,"缺总工时",IF(ROUND($P94-$F94,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="95" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B95" s="28"/>
@@ -11354,6 +12240,10 @@
         <v/>
       </c>
       <c r="R95" s="27"/>
+      <c r="S95" s="21" t="str">
+        <f aca="false">IF($D95="","",IF($B95="","缺月份",IF($F95=0,"缺总工时",IF(ROUND($P95-$F95,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="96" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B96" s="28"/>
@@ -11382,6 +12272,10 @@
         <v/>
       </c>
       <c r="R96" s="27"/>
+      <c r="S96" s="21" t="str">
+        <f aca="false">IF($D96="","",IF($B96="","缺月份",IF($F96=0,"缺总工时",IF(ROUND($P96-$F96,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="97" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B97" s="28"/>
@@ -11410,6 +12304,10 @@
         <v/>
       </c>
       <c r="R97" s="27"/>
+      <c r="S97" s="21" t="str">
+        <f aca="false">IF($D97="","",IF($B97="","缺月份",IF($F97=0,"缺总工时",IF(ROUND($P97-$F97,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="98" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B98" s="28"/>
@@ -11438,6 +12336,10 @@
         <v/>
       </c>
       <c r="R98" s="27"/>
+      <c r="S98" s="21" t="str">
+        <f aca="false">IF($D98="","",IF($B98="","缺月份",IF($F98=0,"缺总工时",IF(ROUND($P98-$F98,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="99" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B99" s="28"/>
@@ -11466,6 +12368,10 @@
         <v/>
       </c>
       <c r="R99" s="27"/>
+      <c r="S99" s="21" t="str">
+        <f aca="false">IF($D99="","",IF($B99="","缺月份",IF($F99=0,"缺总工时",IF(ROUND($P99-$F99,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="100" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B100" s="28"/>
@@ -11494,6 +12400,10 @@
         <v/>
       </c>
       <c r="R100" s="27"/>
+      <c r="S100" s="21" t="str">
+        <f aca="false">IF($D100="","",IF($B100="","缺月份",IF($F100=0,"缺总工时",IF(ROUND($P100-$F100,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="101" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B101" s="28"/>
@@ -11522,6 +12432,10 @@
         <v/>
       </c>
       <c r="R101" s="27"/>
+      <c r="S101" s="21" t="str">
+        <f aca="false">IF($D101="","",IF($B101="","缺月份",IF($F101=0,"缺总工时",IF(ROUND($P101-$F101,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="102" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B102" s="28"/>
@@ -11550,6 +12464,10 @@
         <v/>
       </c>
       <c r="R102" s="27"/>
+      <c r="S102" s="21" t="str">
+        <f aca="false">IF($D102="","",IF($B102="","缺月份",IF($F102=0,"缺总工时",IF(ROUND($P102-$F102,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="103" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B103" s="28"/>
@@ -11578,6 +12496,10 @@
         <v/>
       </c>
       <c r="R103" s="27"/>
+      <c r="S103" s="21" t="str">
+        <f aca="false">IF($D103="","",IF($B103="","缺月份",IF($F103=0,"缺总工时",IF(ROUND($P103-$F103,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="104" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B104" s="28"/>
@@ -11606,6 +12528,10 @@
         <v/>
       </c>
       <c r="R104" s="27"/>
+      <c r="S104" s="21" t="str">
+        <f aca="false">IF($D104="","",IF($B104="","缺月份",IF($F104=0,"缺总工时",IF(ROUND($P104-$F104,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="105" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B105" s="28"/>
@@ -11634,6 +12560,10 @@
         <v/>
       </c>
       <c r="R105" s="27"/>
+      <c r="S105" s="21" t="str">
+        <f aca="false">IF($D105="","",IF($B105="","缺月份",IF($F105=0,"缺总工时",IF(ROUND($P105-$F105,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="106" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B106" s="28"/>
@@ -11662,6 +12592,10 @@
         <v/>
       </c>
       <c r="R106" s="27"/>
+      <c r="S106" s="21" t="str">
+        <f aca="false">IF($D106="","",IF($B106="","缺月份",IF($F106=0,"缺总工时",IF(ROUND($P106-$F106,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="107" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B107" s="28"/>
@@ -11690,6 +12624,10 @@
         <v/>
       </c>
       <c r="R107" s="27"/>
+      <c r="S107" s="21" t="str">
+        <f aca="false">IF($D107="","",IF($B107="","缺月份",IF($F107=0,"缺总工时",IF(ROUND($P107-$F107,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="108" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B108" s="28"/>
@@ -11718,6 +12656,10 @@
         <v/>
       </c>
       <c r="R108" s="27"/>
+      <c r="S108" s="21" t="str">
+        <f aca="false">IF($D108="","",IF($B108="","缺月份",IF($F108=0,"缺总工时",IF(ROUND($P108-$F108,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="109" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B109" s="28"/>
@@ -11746,6 +12688,10 @@
         <v/>
       </c>
       <c r="R109" s="27"/>
+      <c r="S109" s="21" t="str">
+        <f aca="false">IF($D109="","",IF($B109="","缺月份",IF($F109=0,"缺总工时",IF(ROUND($P109-$F109,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="110" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B110" s="28"/>
@@ -11774,6 +12720,10 @@
         <v/>
       </c>
       <c r="R110" s="27"/>
+      <c r="S110" s="21" t="str">
+        <f aca="false">IF($D110="","",IF($B110="","缺月份",IF($F110=0,"缺总工时",IF(ROUND($P110-$F110,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="111" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B111" s="28"/>
@@ -11802,6 +12752,10 @@
         <v/>
       </c>
       <c r="R111" s="27"/>
+      <c r="S111" s="21" t="str">
+        <f aca="false">IF($D111="","",IF($B111="","缺月份",IF($F111=0,"缺总工时",IF(ROUND($P111-$F111,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="112" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B112" s="28"/>
@@ -11830,6 +12784,10 @@
         <v/>
       </c>
       <c r="R112" s="27"/>
+      <c r="S112" s="21" t="str">
+        <f aca="false">IF($D112="","",IF($B112="","缺月份",IF($F112=0,"缺总工时",IF(ROUND($P112-$F112,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="113" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B113" s="28"/>
@@ -11858,6 +12816,10 @@
         <v/>
       </c>
       <c r="R113" s="27"/>
+      <c r="S113" s="21" t="str">
+        <f aca="false">IF($D113="","",IF($B113="","缺月份",IF($F113=0,"缺总工时",IF(ROUND($P113-$F113,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="114" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B114" s="28"/>
@@ -11886,6 +12848,10 @@
         <v/>
       </c>
       <c r="R114" s="27"/>
+      <c r="S114" s="21" t="str">
+        <f aca="false">IF($D114="","",IF($B114="","缺月份",IF($F114=0,"缺总工时",IF(ROUND($P114-$F114,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="115" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B115" s="28"/>
@@ -11914,6 +12880,10 @@
         <v/>
       </c>
       <c r="R115" s="27"/>
+      <c r="S115" s="21" t="str">
+        <f aca="false">IF($D115="","",IF($B115="","缺月份",IF($F115=0,"缺总工时",IF(ROUND($P115-$F115,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="116" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B116" s="28"/>
@@ -11942,6 +12912,10 @@
         <v/>
       </c>
       <c r="R116" s="27"/>
+      <c r="S116" s="21" t="str">
+        <f aca="false">IF($D116="","",IF($B116="","缺月份",IF($F116=0,"缺总工时",IF(ROUND($P116-$F116,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="117" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B117" s="28"/>
@@ -11970,6 +12944,10 @@
         <v/>
       </c>
       <c r="R117" s="27"/>
+      <c r="S117" s="21" t="str">
+        <f aca="false">IF($D117="","",IF($B117="","缺月份",IF($F117=0,"缺总工时",IF(ROUND($P117-$F117,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="118" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B118" s="28"/>
@@ -11998,6 +12976,10 @@
         <v/>
       </c>
       <c r="R118" s="27"/>
+      <c r="S118" s="21" t="str">
+        <f aca="false">IF($D118="","",IF($B118="","缺月份",IF($F118=0,"缺总工时",IF(ROUND($P118-$F118,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="119" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B119" s="28"/>
@@ -12026,6 +13008,10 @@
         <v/>
       </c>
       <c r="R119" s="27"/>
+      <c r="S119" s="21" t="str">
+        <f aca="false">IF($D119="","",IF($B119="","缺月份",IF($F119=0,"缺总工时",IF(ROUND($P119-$F119,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="120" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B120" s="28"/>
@@ -12054,6 +13040,10 @@
         <v/>
       </c>
       <c r="R120" s="27"/>
+      <c r="S120" s="21" t="str">
+        <f aca="false">IF($D120="","",IF($B120="","缺月份",IF($F120=0,"缺总工时",IF(ROUND($P120-$F120,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="121" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B121" s="28"/>
@@ -12082,6 +13072,10 @@
         <v/>
       </c>
       <c r="R121" s="27"/>
+      <c r="S121" s="21" t="str">
+        <f aca="false">IF($D121="","",IF($B121="","缺月份",IF($F121=0,"缺总工时",IF(ROUND($P121-$F121,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="122" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B122" s="28"/>
@@ -12110,6 +13104,10 @@
         <v/>
       </c>
       <c r="R122" s="27"/>
+      <c r="S122" s="21" t="str">
+        <f aca="false">IF($D122="","",IF($B122="","缺月份",IF($F122=0,"缺总工时",IF(ROUND($P122-$F122,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="123" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B123" s="28"/>
@@ -12138,6 +13136,10 @@
         <v/>
       </c>
       <c r="R123" s="27"/>
+      <c r="S123" s="21" t="str">
+        <f aca="false">IF($D123="","",IF($B123="","缺月份",IF($F123=0,"缺总工时",IF(ROUND($P123-$F123,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="124" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B124" s="28"/>
@@ -12166,6 +13168,10 @@
         <v/>
       </c>
       <c r="R124" s="27"/>
+      <c r="S124" s="21" t="str">
+        <f aca="false">IF($D124="","",IF($B124="","缺月份",IF($F124=0,"缺总工时",IF(ROUND($P124-$F124,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="125" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B125" s="28"/>
@@ -12194,6 +13200,10 @@
         <v/>
       </c>
       <c r="R125" s="27"/>
+      <c r="S125" s="21" t="str">
+        <f aca="false">IF($D125="","",IF($B125="","缺月份",IF($F125=0,"缺总工时",IF(ROUND($P125-$F125,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="126" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B126" s="28"/>
@@ -12222,6 +13232,10 @@
         <v/>
       </c>
       <c r="R126" s="27"/>
+      <c r="S126" s="21" t="str">
+        <f aca="false">IF($D126="","",IF($B126="","缺月份",IF($F126=0,"缺总工时",IF(ROUND($P126-$F126,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="127" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B127" s="28"/>
@@ -12250,6 +13264,10 @@
         <v/>
       </c>
       <c r="R127" s="27"/>
+      <c r="S127" s="21" t="str">
+        <f aca="false">IF($D127="","",IF($B127="","缺月份",IF($F127=0,"缺总工时",IF(ROUND($P127-$F127,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="128" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B128" s="28"/>
@@ -12278,6 +13296,10 @@
         <v/>
       </c>
       <c r="R128" s="27"/>
+      <c r="S128" s="21" t="str">
+        <f aca="false">IF($D128="","",IF($B128="","缺月份",IF($F128=0,"缺总工时",IF(ROUND($P128-$F128,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="129" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B129" s="28"/>
@@ -12306,6 +13328,10 @@
         <v/>
       </c>
       <c r="R129" s="27"/>
+      <c r="S129" s="21" t="str">
+        <f aca="false">IF($D129="","",IF($B129="","缺月份",IF($F129=0,"缺总工时",IF(ROUND($P129-$F129,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="130" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B130" s="28"/>
@@ -12334,6 +13360,10 @@
         <v/>
       </c>
       <c r="R130" s="27"/>
+      <c r="S130" s="21" t="str">
+        <f aca="false">IF($D130="","",IF($B130="","缺月份",IF($F130=0,"缺总工时",IF(ROUND($P130-$F130,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="131" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B131" s="28"/>
@@ -12362,6 +13392,10 @@
         <v/>
       </c>
       <c r="R131" s="27"/>
+      <c r="S131" s="21" t="str">
+        <f aca="false">IF($D131="","",IF($B131="","缺月份",IF($F131=0,"缺总工时",IF(ROUND($P131-$F131,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="132" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B132" s="28"/>
@@ -12390,6 +13424,10 @@
         <v/>
       </c>
       <c r="R132" s="27"/>
+      <c r="S132" s="21" t="str">
+        <f aca="false">IF($D132="","",IF($B132="","缺月份",IF($F132=0,"缺总工时",IF(ROUND($P132-$F132,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="133" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B133" s="28"/>
@@ -12418,6 +13456,10 @@
         <v/>
       </c>
       <c r="R133" s="27"/>
+      <c r="S133" s="21" t="str">
+        <f aca="false">IF($D133="","",IF($B133="","缺月份",IF($F133=0,"缺总工时",IF(ROUND($P133-$F133,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="134" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B134" s="28"/>
@@ -12446,6 +13488,10 @@
         <v/>
       </c>
       <c r="R134" s="27"/>
+      <c r="S134" s="21" t="str">
+        <f aca="false">IF($D134="","",IF($B134="","缺月份",IF($F134=0,"缺总工时",IF(ROUND($P134-$F134,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="135" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B135" s="28"/>
@@ -12474,6 +13520,10 @@
         <v/>
       </c>
       <c r="R135" s="27"/>
+      <c r="S135" s="21" t="str">
+        <f aca="false">IF($D135="","",IF($B135="","缺月份",IF($F135=0,"缺总工时",IF(ROUND($P135-$F135,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="136" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B136" s="28"/>
@@ -12502,6 +13552,10 @@
         <v/>
       </c>
       <c r="R136" s="27"/>
+      <c r="S136" s="21" t="str">
+        <f aca="false">IF($D136="","",IF($B136="","缺月份",IF($F136=0,"缺总工时",IF(ROUND($P136-$F136,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="137" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B137" s="28"/>
@@ -12530,6 +13584,10 @@
         <v/>
       </c>
       <c r="R137" s="27"/>
+      <c r="S137" s="21" t="str">
+        <f aca="false">IF($D137="","",IF($B137="","缺月份",IF($F137=0,"缺总工时",IF(ROUND($P137-$F137,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="138" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B138" s="28"/>
@@ -12558,6 +13616,10 @@
         <v/>
       </c>
       <c r="R138" s="27"/>
+      <c r="S138" s="21" t="str">
+        <f aca="false">IF($D138="","",IF($B138="","缺月份",IF($F138=0,"缺总工时",IF(ROUND($P138-$F138,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="139" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B139" s="28"/>
@@ -12586,6 +13648,10 @@
         <v/>
       </c>
       <c r="R139" s="27"/>
+      <c r="S139" s="21" t="str">
+        <f aca="false">IF($D139="","",IF($B139="","缺月份",IF($F139=0,"缺总工时",IF(ROUND($P139-$F139,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="140" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B140" s="28"/>
@@ -12614,6 +13680,10 @@
         <v/>
       </c>
       <c r="R140" s="27"/>
+      <c r="S140" s="21" t="str">
+        <f aca="false">IF($D140="","",IF($B140="","缺月份",IF($F140=0,"缺总工时",IF(ROUND($P140-$F140,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="141" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B141" s="28"/>
@@ -12642,6 +13712,10 @@
         <v/>
       </c>
       <c r="R141" s="27"/>
+      <c r="S141" s="21" t="str">
+        <f aca="false">IF($D141="","",IF($B141="","缺月份",IF($F141=0,"缺总工时",IF(ROUND($P141-$F141,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="142" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B142" s="28"/>
@@ -12670,6 +13744,10 @@
         <v/>
       </c>
       <c r="R142" s="27"/>
+      <c r="S142" s="21" t="str">
+        <f aca="false">IF($D142="","",IF($B142="","缺月份",IF($F142=0,"缺总工时",IF(ROUND($P142-$F142,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="143" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B143" s="28"/>
@@ -12698,6 +13776,10 @@
         <v/>
       </c>
       <c r="R143" s="27"/>
+      <c r="S143" s="21" t="str">
+        <f aca="false">IF($D143="","",IF($B143="","缺月份",IF($F143=0,"缺总工时",IF(ROUND($P143-$F143,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="144" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B144" s="28"/>
@@ -12726,6 +13808,10 @@
         <v/>
       </c>
       <c r="R144" s="27"/>
+      <c r="S144" s="21" t="str">
+        <f aca="false">IF($D144="","",IF($B144="","缺月份",IF($F144=0,"缺总工时",IF(ROUND($P144-$F144,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="145" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B145" s="28"/>
@@ -12754,6 +13840,10 @@
         <v/>
       </c>
       <c r="R145" s="27"/>
+      <c r="S145" s="21" t="str">
+        <f aca="false">IF($D145="","",IF($B145="","缺月份",IF($F145=0,"缺总工时",IF(ROUND($P145-$F145,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="146" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B146" s="28"/>
@@ -12782,6 +13872,10 @@
         <v/>
       </c>
       <c r="R146" s="27"/>
+      <c r="S146" s="21" t="str">
+        <f aca="false">IF($D146="","",IF($B146="","缺月份",IF($F146=0,"缺总工时",IF(ROUND($P146-$F146,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="147" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B147" s="28"/>
@@ -12810,6 +13904,10 @@
         <v/>
       </c>
       <c r="R147" s="27"/>
+      <c r="S147" s="21" t="str">
+        <f aca="false">IF($D147="","",IF($B147="","缺月份",IF($F147=0,"缺总工时",IF(ROUND($P147-$F147,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="148" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B148" s="28"/>
@@ -12838,6 +13936,10 @@
         <v/>
       </c>
       <c r="R148" s="27"/>
+      <c r="S148" s="21" t="str">
+        <f aca="false">IF($D148="","",IF($B148="","缺月份",IF($F148=0,"缺总工时",IF(ROUND($P148-$F148,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="149" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B149" s="28"/>
@@ -12866,6 +13968,10 @@
         <v/>
       </c>
       <c r="R149" s="27"/>
+      <c r="S149" s="21" t="str">
+        <f aca="false">IF($D149="","",IF($B149="","缺月份",IF($F149=0,"缺总工时",IF(ROUND($P149-$F149,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="150" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B150" s="28"/>
@@ -12894,10 +14000,14 @@
         <v/>
       </c>
       <c r="R150" s="27"/>
+      <c r="S150" s="21" t="str">
+        <f aca="false">IF($D150="","",IF($B150="","缺月份",IF($F150=0,"缺总工时",IF(ROUND($P150-$F150,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B2:R2"/>
+  <mergeCells count="12">
+    <mergeCell ref="B2:S2"/>
     <mergeCell ref="B4:B6"/>
     <mergeCell ref="C4:C6"/>
     <mergeCell ref="D4:D6"/>
@@ -12906,6 +14016,7 @@
     <mergeCell ref="G4:G6"/>
     <mergeCell ref="H4:P4"/>
     <mergeCell ref="R4:R6"/>
+    <mergeCell ref="S4:S6"/>
     <mergeCell ref="P5:P6"/>
     <mergeCell ref="Q5:Q6"/>
   </mergeCells>
@@ -12930,7 +14041,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:R102"/>
+  <dimension ref="B2:S102"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -12940,11 +14051,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="6" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="11"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -12962,36 +14074,37 @@
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q3" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="R3" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I4" s="15"/>
       <c r="J4" s="15"/>
@@ -13002,10 +14115,13 @@
       <c r="O4" s="15"/>
       <c r="P4" s="15"/>
       <c r="Q4" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="R4" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="S4" s="14" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13048,12 +14164,13 @@
         <v>RD08</v>
       </c>
       <c r="P5" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q5" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="R5" s="14"/>
+      <c r="S5" s="14"/>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="14"/>
@@ -13097,6 +14214,7 @@
       <c r="P6" s="14"/>
       <c r="Q6" s="14"/>
       <c r="R6" s="14"/>
+      <c r="S6" s="14"/>
     </row>
     <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="28" t="n">
@@ -13106,10 +14224,10 @@
         <v>1</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F7" s="18" t="n">
         <v>180</v>
@@ -13143,7 +14261,11 @@
         <v>0.8</v>
       </c>
       <c r="R7" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="S7" s="21" t="str">
+        <f aca="false">IF($D7="","",IF($B7="","缺月份",IF($F7=0,"缺总工时",IF(ROUND($P7-$F7,2)&gt;0,"工时超出","√"))))</f>
+        <v>√</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13154,10 +14276,10 @@
         <v>2</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F8" s="18" t="n">
         <v>180</v>
@@ -13191,6 +14313,10 @@
         <v>0.8</v>
       </c>
       <c r="R8" s="27"/>
+      <c r="S8" s="21" t="str">
+        <f aca="false">IF($D8="","",IF($B8="","缺月份",IF($F8=0,"缺总工时",IF(ROUND($P8-$F8,2)&gt;0,"工时超出","√"))))</f>
+        <v>√</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="28" t="n">
@@ -13200,10 +14326,10 @@
         <v>3</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F9" s="18" t="n">
         <v>180</v>
@@ -13235,6 +14361,10 @@
         <v>0.6</v>
       </c>
       <c r="R9" s="27"/>
+      <c r="S9" s="21" t="str">
+        <f aca="false">IF($D9="","",IF($B9="","缺月份",IF($F9=0,"缺总工时",IF(ROUND($P9-$F9,2)&gt;0,"工时超出","√"))))</f>
+        <v>√</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="28" t="n">
@@ -13244,10 +14374,10 @@
         <v>4</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F10" s="18" t="n">
         <v>180</v>
@@ -13277,6 +14407,10 @@
         <v>0.4</v>
       </c>
       <c r="R10" s="27"/>
+      <c r="S10" s="21" t="str">
+        <f aca="false">IF($D10="","",IF($B10="","缺月份",IF($F10=0,"缺总工时",IF(ROUND($P10-$F10,2)&gt;0,"工时超出","√"))))</f>
+        <v>√</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="28" t="n">
@@ -13286,10 +14420,10 @@
         <v>5</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F11" s="18" t="n">
         <v>180</v>
@@ -13319,6 +14453,10 @@
         <v>0.4</v>
       </c>
       <c r="R11" s="27"/>
+      <c r="S11" s="21" t="str">
+        <f aca="false">IF($D11="","",IF($B11="","缺月份",IF($F11=0,"缺总工时",IF(ROUND($P11-$F11,2)&gt;0,"工时超出","√"))))</f>
+        <v>√</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="28" t="n">
@@ -13328,10 +14466,10 @@
         <v>6</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F12" s="18" t="n">
         <v>180</v>
@@ -13359,6 +14497,10 @@
         <v>0.2</v>
       </c>
       <c r="R12" s="27"/>
+      <c r="S12" s="21" t="str">
+        <f aca="false">IF($D12="","",IF($B12="","缺月份",IF($F12=0,"缺总工时",IF(ROUND($P12-$F12,2)&gt;0,"工时超出","√"))))</f>
+        <v>√</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="28"/>
@@ -13387,6 +14529,10 @@
         <v/>
       </c>
       <c r="R13" s="27"/>
+      <c r="S13" s="21" t="str">
+        <f aca="false">IF($D13="","",IF($B13="","缺月份",IF($F13=0,"缺总工时",IF(ROUND($P13-$F13,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="28"/>
@@ -13415,6 +14561,10 @@
         <v/>
       </c>
       <c r="R14" s="27"/>
+      <c r="S14" s="21" t="str">
+        <f aca="false">IF($D14="","",IF($B14="","缺月份",IF($F14=0,"缺总工时",IF(ROUND($P14-$F14,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="28"/>
@@ -13443,6 +14593,10 @@
         <v/>
       </c>
       <c r="R15" s="27"/>
+      <c r="S15" s="21" t="str">
+        <f aca="false">IF($D15="","",IF($B15="","缺月份",IF($F15=0,"缺总工时",IF(ROUND($P15-$F15,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="28"/>
@@ -13471,6 +14625,10 @@
         <v/>
       </c>
       <c r="R16" s="27"/>
+      <c r="S16" s="21" t="str">
+        <f aca="false">IF($D16="","",IF($B16="","缺月份",IF($F16=0,"缺总工时",IF(ROUND($P16-$F16,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="28"/>
@@ -13499,6 +14657,10 @@
         <v/>
       </c>
       <c r="R17" s="27"/>
+      <c r="S17" s="21" t="str">
+        <f aca="false">IF($D17="","",IF($B17="","缺月份",IF($F17=0,"缺总工时",IF(ROUND($P17-$F17,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="28"/>
@@ -13527,6 +14689,10 @@
         <v/>
       </c>
       <c r="R18" s="27"/>
+      <c r="S18" s="21" t="str">
+        <f aca="false">IF($D18="","",IF($B18="","缺月份",IF($F18=0,"缺总工时",IF(ROUND($P18-$F18,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="28"/>
@@ -13555,6 +14721,10 @@
         <v/>
       </c>
       <c r="R19" s="27"/>
+      <c r="S19" s="21" t="str">
+        <f aca="false">IF($D19="","",IF($B19="","缺月份",IF($F19=0,"缺总工时",IF(ROUND($P19-$F19,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="28"/>
@@ -13583,6 +14753,10 @@
         <v/>
       </c>
       <c r="R20" s="27"/>
+      <c r="S20" s="21" t="str">
+        <f aca="false">IF($D20="","",IF($B20="","缺月份",IF($F20=0,"缺总工时",IF(ROUND($P20-$F20,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="28"/>
@@ -13611,6 +14785,10 @@
         <v/>
       </c>
       <c r="R21" s="27"/>
+      <c r="S21" s="21" t="str">
+        <f aca="false">IF($D21="","",IF($B21="","缺月份",IF($F21=0,"缺总工时",IF(ROUND($P21-$F21,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="28"/>
@@ -13639,6 +14817,10 @@
         <v/>
       </c>
       <c r="R22" s="27"/>
+      <c r="S22" s="21" t="str">
+        <f aca="false">IF($D22="","",IF($B22="","缺月份",IF($F22=0,"缺总工时",IF(ROUND($P22-$F22,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="28"/>
@@ -13667,6 +14849,10 @@
         <v/>
       </c>
       <c r="R23" s="27"/>
+      <c r="S23" s="21" t="str">
+        <f aca="false">IF($D23="","",IF($B23="","缺月份",IF($F23=0,"缺总工时",IF(ROUND($P23-$F23,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="28"/>
@@ -13695,6 +14881,10 @@
         <v/>
       </c>
       <c r="R24" s="27"/>
+      <c r="S24" s="21" t="str">
+        <f aca="false">IF($D24="","",IF($B24="","缺月份",IF($F24=0,"缺总工时",IF(ROUND($P24-$F24,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="28"/>
@@ -13723,6 +14913,10 @@
         <v/>
       </c>
       <c r="R25" s="27"/>
+      <c r="S25" s="21" t="str">
+        <f aca="false">IF($D25="","",IF($B25="","缺月份",IF($F25=0,"缺总工时",IF(ROUND($P25-$F25,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="28"/>
@@ -13751,6 +14945,10 @@
         <v/>
       </c>
       <c r="R26" s="27"/>
+      <c r="S26" s="21" t="str">
+        <f aca="false">IF($D26="","",IF($B26="","缺月份",IF($F26=0,"缺总工时",IF(ROUND($P26-$F26,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="28"/>
@@ -13779,6 +14977,10 @@
         <v/>
       </c>
       <c r="R27" s="27"/>
+      <c r="S27" s="21" t="str">
+        <f aca="false">IF($D27="","",IF($B27="","缺月份",IF($F27=0,"缺总工时",IF(ROUND($P27-$F27,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="28"/>
@@ -13807,6 +15009,10 @@
         <v/>
       </c>
       <c r="R28" s="27"/>
+      <c r="S28" s="21" t="str">
+        <f aca="false">IF($D28="","",IF($B28="","缺月份",IF($F28=0,"缺总工时",IF(ROUND($P28-$F28,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="28"/>
@@ -13835,6 +15041,10 @@
         <v/>
       </c>
       <c r="R29" s="27"/>
+      <c r="S29" s="21" t="str">
+        <f aca="false">IF($D29="","",IF($B29="","缺月份",IF($F29=0,"缺总工时",IF(ROUND($P29-$F29,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="28"/>
@@ -13863,6 +15073,10 @@
         <v/>
       </c>
       <c r="R30" s="27"/>
+      <c r="S30" s="21" t="str">
+        <f aca="false">IF($D30="","",IF($B30="","缺月份",IF($F30=0,"缺总工时",IF(ROUND($P30-$F30,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="28"/>
@@ -13891,6 +15105,10 @@
         <v/>
       </c>
       <c r="R31" s="27"/>
+      <c r="S31" s="21" t="str">
+        <f aca="false">IF($D31="","",IF($B31="","缺月份",IF($F31=0,"缺总工时",IF(ROUND($P31-$F31,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="28"/>
@@ -13919,6 +15137,10 @@
         <v/>
       </c>
       <c r="R32" s="27"/>
+      <c r="S32" s="21" t="str">
+        <f aca="false">IF($D32="","",IF($B32="","缺月份",IF($F32=0,"缺总工时",IF(ROUND($P32-$F32,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="28"/>
@@ -13947,6 +15169,10 @@
         <v/>
       </c>
       <c r="R33" s="27"/>
+      <c r="S33" s="21" t="str">
+        <f aca="false">IF($D33="","",IF($B33="","缺月份",IF($F33=0,"缺总工时",IF(ROUND($P33-$F33,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="28"/>
@@ -13975,6 +15201,10 @@
         <v/>
       </c>
       <c r="R34" s="27"/>
+      <c r="S34" s="21" t="str">
+        <f aca="false">IF($D34="","",IF($B34="","缺月份",IF($F34=0,"缺总工时",IF(ROUND($P34-$F34,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="28"/>
@@ -14003,6 +15233,10 @@
         <v/>
       </c>
       <c r="R35" s="27"/>
+      <c r="S35" s="21" t="str">
+        <f aca="false">IF($D35="","",IF($B35="","缺月份",IF($F35=0,"缺总工时",IF(ROUND($P35-$F35,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="28"/>
@@ -14031,6 +15265,10 @@
         <v/>
       </c>
       <c r="R36" s="27"/>
+      <c r="S36" s="21" t="str">
+        <f aca="false">IF($D36="","",IF($B36="","缺月份",IF($F36=0,"缺总工时",IF(ROUND($P36-$F36,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="28"/>
@@ -14059,6 +15297,10 @@
         <v/>
       </c>
       <c r="R37" s="27"/>
+      <c r="S37" s="21" t="str">
+        <f aca="false">IF($D37="","",IF($B37="","缺月份",IF($F37=0,"缺总工时",IF(ROUND($P37-$F37,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="28"/>
@@ -14087,6 +15329,10 @@
         <v/>
       </c>
       <c r="R38" s="27"/>
+      <c r="S38" s="21" t="str">
+        <f aca="false">IF($D38="","",IF($B38="","缺月份",IF($F38=0,"缺总工时",IF(ROUND($P38-$F38,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="28"/>
@@ -14115,6 +15361,10 @@
         <v/>
       </c>
       <c r="R39" s="27"/>
+      <c r="S39" s="21" t="str">
+        <f aca="false">IF($D39="","",IF($B39="","缺月份",IF($F39=0,"缺总工时",IF(ROUND($P39-$F39,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="28"/>
@@ -14143,6 +15393,10 @@
         <v/>
       </c>
       <c r="R40" s="27"/>
+      <c r="S40" s="21" t="str">
+        <f aca="false">IF($D40="","",IF($B40="","缺月份",IF($F40=0,"缺总工时",IF(ROUND($P40-$F40,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="28"/>
@@ -14171,6 +15425,10 @@
         <v/>
       </c>
       <c r="R41" s="27"/>
+      <c r="S41" s="21" t="str">
+        <f aca="false">IF($D41="","",IF($B41="","缺月份",IF($F41=0,"缺总工时",IF(ROUND($P41-$F41,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="28"/>
@@ -14199,6 +15457,10 @@
         <v/>
       </c>
       <c r="R42" s="27"/>
+      <c r="S42" s="21" t="str">
+        <f aca="false">IF($D42="","",IF($B42="","缺月份",IF($F42=0,"缺总工时",IF(ROUND($P42-$F42,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="28"/>
@@ -14227,6 +15489,10 @@
         <v/>
       </c>
       <c r="R43" s="27"/>
+      <c r="S43" s="21" t="str">
+        <f aca="false">IF($D43="","",IF($B43="","缺月份",IF($F43=0,"缺总工时",IF(ROUND($P43-$F43,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="28"/>
@@ -14255,6 +15521,10 @@
         <v/>
       </c>
       <c r="R44" s="27"/>
+      <c r="S44" s="21" t="str">
+        <f aca="false">IF($D44="","",IF($B44="","缺月份",IF($F44=0,"缺总工时",IF(ROUND($P44-$F44,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="28"/>
@@ -14283,6 +15553,10 @@
         <v/>
       </c>
       <c r="R45" s="27"/>
+      <c r="S45" s="21" t="str">
+        <f aca="false">IF($D45="","",IF($B45="","缺月份",IF($F45=0,"缺总工时",IF(ROUND($P45-$F45,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="28"/>
@@ -14311,6 +15585,10 @@
         <v/>
       </c>
       <c r="R46" s="27"/>
+      <c r="S46" s="21" t="str">
+        <f aca="false">IF($D46="","",IF($B46="","缺月份",IF($F46=0,"缺总工时",IF(ROUND($P46-$F46,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="28"/>
@@ -14339,6 +15617,10 @@
         <v/>
       </c>
       <c r="R47" s="27"/>
+      <c r="S47" s="21" t="str">
+        <f aca="false">IF($D47="","",IF($B47="","缺月份",IF($F47=0,"缺总工时",IF(ROUND($P47-$F47,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="28"/>
@@ -14367,6 +15649,10 @@
         <v/>
       </c>
       <c r="R48" s="27"/>
+      <c r="S48" s="21" t="str">
+        <f aca="false">IF($D48="","",IF($B48="","缺月份",IF($F48=0,"缺总工时",IF(ROUND($P48-$F48,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="28"/>
@@ -14395,6 +15681,10 @@
         <v/>
       </c>
       <c r="R49" s="27"/>
+      <c r="S49" s="21" t="str">
+        <f aca="false">IF($D49="","",IF($B49="","缺月份",IF($F49=0,"缺总工时",IF(ROUND($P49-$F49,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="28"/>
@@ -14423,6 +15713,10 @@
         <v/>
       </c>
       <c r="R50" s="27"/>
+      <c r="S50" s="21" t="str">
+        <f aca="false">IF($D50="","",IF($B50="","缺月份",IF($F50=0,"缺总工时",IF(ROUND($P50-$F50,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="28"/>
@@ -14451,6 +15745,10 @@
         <v/>
       </c>
       <c r="R51" s="27"/>
+      <c r="S51" s="21" t="str">
+        <f aca="false">IF($D51="","",IF($B51="","缺月份",IF($F51=0,"缺总工时",IF(ROUND($P51-$F51,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="28"/>
@@ -14479,6 +15777,10 @@
         <v/>
       </c>
       <c r="R52" s="27"/>
+      <c r="S52" s="21" t="str">
+        <f aca="false">IF($D52="","",IF($B52="","缺月份",IF($F52=0,"缺总工时",IF(ROUND($P52-$F52,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="28"/>
@@ -14507,6 +15809,10 @@
         <v/>
       </c>
       <c r="R53" s="27"/>
+      <c r="S53" s="21" t="str">
+        <f aca="false">IF($D53="","",IF($B53="","缺月份",IF($F53=0,"缺总工时",IF(ROUND($P53-$F53,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="28"/>
@@ -14535,6 +15841,10 @@
         <v/>
       </c>
       <c r="R54" s="27"/>
+      <c r="S54" s="21" t="str">
+        <f aca="false">IF($D54="","",IF($B54="","缺月份",IF($F54=0,"缺总工时",IF(ROUND($P54-$F54,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="28"/>
@@ -14563,6 +15873,10 @@
         <v/>
       </c>
       <c r="R55" s="27"/>
+      <c r="S55" s="21" t="str">
+        <f aca="false">IF($D55="","",IF($B55="","缺月份",IF($F55=0,"缺总工时",IF(ROUND($P55-$F55,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="28"/>
@@ -14591,6 +15905,10 @@
         <v/>
       </c>
       <c r="R56" s="27"/>
+      <c r="S56" s="21" t="str">
+        <f aca="false">IF($D56="","",IF($B56="","缺月份",IF($F56=0,"缺总工时",IF(ROUND($P56-$F56,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="28"/>
@@ -14619,6 +15937,10 @@
         <v/>
       </c>
       <c r="R57" s="27"/>
+      <c r="S57" s="21" t="str">
+        <f aca="false">IF($D57="","",IF($B57="","缺月份",IF($F57=0,"缺总工时",IF(ROUND($P57-$F57,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="28"/>
@@ -14647,6 +15969,10 @@
         <v/>
       </c>
       <c r="R58" s="27"/>
+      <c r="S58" s="21" t="str">
+        <f aca="false">IF($D58="","",IF($B58="","缺月份",IF($F58=0,"缺总工时",IF(ROUND($P58-$F58,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="28"/>
@@ -14675,6 +16001,10 @@
         <v/>
       </c>
       <c r="R59" s="27"/>
+      <c r="S59" s="21" t="str">
+        <f aca="false">IF($D59="","",IF($B59="","缺月份",IF($F59=0,"缺总工时",IF(ROUND($P59-$F59,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="28"/>
@@ -14703,6 +16033,10 @@
         <v/>
       </c>
       <c r="R60" s="27"/>
+      <c r="S60" s="21" t="str">
+        <f aca="false">IF($D60="","",IF($B60="","缺月份",IF($F60=0,"缺总工时",IF(ROUND($P60-$F60,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="28"/>
@@ -14731,6 +16065,10 @@
         <v/>
       </c>
       <c r="R61" s="27"/>
+      <c r="S61" s="21" t="str">
+        <f aca="false">IF($D61="","",IF($B61="","缺月份",IF($F61=0,"缺总工时",IF(ROUND($P61-$F61,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="28"/>
@@ -14759,6 +16097,10 @@
         <v/>
       </c>
       <c r="R62" s="27"/>
+      <c r="S62" s="21" t="str">
+        <f aca="false">IF($D62="","",IF($B62="","缺月份",IF($F62=0,"缺总工时",IF(ROUND($P62-$F62,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="28"/>
@@ -14787,6 +16129,10 @@
         <v/>
       </c>
       <c r="R63" s="27"/>
+      <c r="S63" s="21" t="str">
+        <f aca="false">IF($D63="","",IF($B63="","缺月份",IF($F63=0,"缺总工时",IF(ROUND($P63-$F63,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="28"/>
@@ -14815,6 +16161,10 @@
         <v/>
       </c>
       <c r="R64" s="27"/>
+      <c r="S64" s="21" t="str">
+        <f aca="false">IF($D64="","",IF($B64="","缺月份",IF($F64=0,"缺总工时",IF(ROUND($P64-$F64,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="28"/>
@@ -14843,6 +16193,10 @@
         <v/>
       </c>
       <c r="R65" s="27"/>
+      <c r="S65" s="21" t="str">
+        <f aca="false">IF($D65="","",IF($B65="","缺月份",IF($F65=0,"缺总工时",IF(ROUND($P65-$F65,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="28"/>
@@ -14871,6 +16225,10 @@
         <v/>
       </c>
       <c r="R66" s="27"/>
+      <c r="S66" s="21" t="str">
+        <f aca="false">IF($D66="","",IF($B66="","缺月份",IF($F66=0,"缺总工时",IF(ROUND($P66-$F66,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="28"/>
@@ -14899,6 +16257,10 @@
         <v/>
       </c>
       <c r="R67" s="27"/>
+      <c r="S67" s="21" t="str">
+        <f aca="false">IF($D67="","",IF($B67="","缺月份",IF($F67=0,"缺总工时",IF(ROUND($P67-$F67,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="28"/>
@@ -14927,6 +16289,10 @@
         <v/>
       </c>
       <c r="R68" s="27"/>
+      <c r="S68" s="21" t="str">
+        <f aca="false">IF($D68="","",IF($B68="","缺月份",IF($F68=0,"缺总工时",IF(ROUND($P68-$F68,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="28"/>
@@ -14955,6 +16321,10 @@
         <v/>
       </c>
       <c r="R69" s="27"/>
+      <c r="S69" s="21" t="str">
+        <f aca="false">IF($D69="","",IF($B69="","缺月份",IF($F69=0,"缺总工时",IF(ROUND($P69-$F69,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="28"/>
@@ -14983,6 +16353,10 @@
         <v/>
       </c>
       <c r="R70" s="27"/>
+      <c r="S70" s="21" t="str">
+        <f aca="false">IF($D70="","",IF($B70="","缺月份",IF($F70=0,"缺总工时",IF(ROUND($P70-$F70,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="28"/>
@@ -15011,6 +16385,10 @@
         <v/>
       </c>
       <c r="R71" s="27"/>
+      <c r="S71" s="21" t="str">
+        <f aca="false">IF($D71="","",IF($B71="","缺月份",IF($F71=0,"缺总工时",IF(ROUND($P71-$F71,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="28"/>
@@ -15039,6 +16417,10 @@
         <v/>
       </c>
       <c r="R72" s="27"/>
+      <c r="S72" s="21" t="str">
+        <f aca="false">IF($D72="","",IF($B72="","缺月份",IF($F72=0,"缺总工时",IF(ROUND($P72-$F72,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="28"/>
@@ -15067,6 +16449,10 @@
         <v/>
       </c>
       <c r="R73" s="27"/>
+      <c r="S73" s="21" t="str">
+        <f aca="false">IF($D73="","",IF($B73="","缺月份",IF($F73=0,"缺总工时",IF(ROUND($P73-$F73,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="28"/>
@@ -15095,6 +16481,10 @@
         <v/>
       </c>
       <c r="R74" s="27"/>
+      <c r="S74" s="21" t="str">
+        <f aca="false">IF($D74="","",IF($B74="","缺月份",IF($F74=0,"缺总工时",IF(ROUND($P74-$F74,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="28"/>
@@ -15123,6 +16513,10 @@
         <v/>
       </c>
       <c r="R75" s="27"/>
+      <c r="S75" s="21" t="str">
+        <f aca="false">IF($D75="","",IF($B75="","缺月份",IF($F75=0,"缺总工时",IF(ROUND($P75-$F75,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="28"/>
@@ -15151,6 +16545,10 @@
         <v/>
       </c>
       <c r="R76" s="27"/>
+      <c r="S76" s="21" t="str">
+        <f aca="false">IF($D76="","",IF($B76="","缺月份",IF($F76=0,"缺总工时",IF(ROUND($P76-$F76,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="28"/>
@@ -15179,6 +16577,10 @@
         <v/>
       </c>
       <c r="R77" s="27"/>
+      <c r="S77" s="21" t="str">
+        <f aca="false">IF($D77="","",IF($B77="","缺月份",IF($F77=0,"缺总工时",IF(ROUND($P77-$F77,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="28"/>
@@ -15207,6 +16609,10 @@
         <v/>
       </c>
       <c r="R78" s="27"/>
+      <c r="S78" s="21" t="str">
+        <f aca="false">IF($D78="","",IF($B78="","缺月份",IF($F78=0,"缺总工时",IF(ROUND($P78-$F78,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="28"/>
@@ -15235,6 +16641,10 @@
         <v/>
       </c>
       <c r="R79" s="27"/>
+      <c r="S79" s="21" t="str">
+        <f aca="false">IF($D79="","",IF($B79="","缺月份",IF($F79=0,"缺总工时",IF(ROUND($P79-$F79,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="28"/>
@@ -15263,6 +16673,10 @@
         <v/>
       </c>
       <c r="R80" s="27"/>
+      <c r="S80" s="21" t="str">
+        <f aca="false">IF($D80="","",IF($B80="","缺月份",IF($F80=0,"缺总工时",IF(ROUND($P80-$F80,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="81" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="28"/>
@@ -15291,6 +16705,10 @@
         <v/>
       </c>
       <c r="R81" s="27"/>
+      <c r="S81" s="21" t="str">
+        <f aca="false">IF($D81="","",IF($B81="","缺月份",IF($F81=0,"缺总工时",IF(ROUND($P81-$F81,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="82" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="28"/>
@@ -15319,6 +16737,10 @@
         <v/>
       </c>
       <c r="R82" s="27"/>
+      <c r="S82" s="21" t="str">
+        <f aca="false">IF($D82="","",IF($B82="","缺月份",IF($F82=0,"缺总工时",IF(ROUND($P82-$F82,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="28"/>
@@ -15347,6 +16769,10 @@
         <v/>
       </c>
       <c r="R83" s="27"/>
+      <c r="S83" s="21" t="str">
+        <f aca="false">IF($D83="","",IF($B83="","缺月份",IF($F83=0,"缺总工时",IF(ROUND($P83-$F83,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B84" s="28"/>
@@ -15375,6 +16801,10 @@
         <v/>
       </c>
       <c r="R84" s="27"/>
+      <c r="S84" s="21" t="str">
+        <f aca="false">IF($D84="","",IF($B84="","缺月份",IF($F84=0,"缺总工时",IF(ROUND($P84-$F84,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="85" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="28"/>
@@ -15403,6 +16833,10 @@
         <v/>
       </c>
       <c r="R85" s="27"/>
+      <c r="S85" s="21" t="str">
+        <f aca="false">IF($D85="","",IF($B85="","缺月份",IF($F85=0,"缺总工时",IF(ROUND($P85-$F85,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="86" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="28"/>
@@ -15431,6 +16865,10 @@
         <v/>
       </c>
       <c r="R86" s="27"/>
+      <c r="S86" s="21" t="str">
+        <f aca="false">IF($D86="","",IF($B86="","缺月份",IF($F86=0,"缺总工时",IF(ROUND($P86-$F86,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B87" s="28"/>
@@ -15459,6 +16897,10 @@
         <v/>
       </c>
       <c r="R87" s="27"/>
+      <c r="S87" s="21" t="str">
+        <f aca="false">IF($D87="","",IF($B87="","缺月份",IF($F87=0,"缺总工时",IF(ROUND($P87-$F87,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="88" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B88" s="28"/>
@@ -15487,6 +16929,10 @@
         <v/>
       </c>
       <c r="R88" s="27"/>
+      <c r="S88" s="21" t="str">
+        <f aca="false">IF($D88="","",IF($B88="","缺月份",IF($F88=0,"缺总工时",IF(ROUND($P88-$F88,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="89" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B89" s="28"/>
@@ -15515,6 +16961,10 @@
         <v/>
       </c>
       <c r="R89" s="27"/>
+      <c r="S89" s="21" t="str">
+        <f aca="false">IF($D89="","",IF($B89="","缺月份",IF($F89=0,"缺总工时",IF(ROUND($P89-$F89,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="90" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B90" s="28"/>
@@ -15543,6 +16993,10 @@
         <v/>
       </c>
       <c r="R90" s="27"/>
+      <c r="S90" s="21" t="str">
+        <f aca="false">IF($D90="","",IF($B90="","缺月份",IF($F90=0,"缺总工时",IF(ROUND($P90-$F90,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="91" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B91" s="28"/>
@@ -15571,6 +17025,10 @@
         <v/>
       </c>
       <c r="R91" s="27"/>
+      <c r="S91" s="21" t="str">
+        <f aca="false">IF($D91="","",IF($B91="","缺月份",IF($F91=0,"缺总工时",IF(ROUND($P91-$F91,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B92" s="28"/>
@@ -15599,6 +17057,10 @@
         <v/>
       </c>
       <c r="R92" s="27"/>
+      <c r="S92" s="21" t="str">
+        <f aca="false">IF($D92="","",IF($B92="","缺月份",IF($F92=0,"缺总工时",IF(ROUND($P92-$F92,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="93" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B93" s="28"/>
@@ -15627,6 +17089,10 @@
         <v/>
       </c>
       <c r="R93" s="27"/>
+      <c r="S93" s="21" t="str">
+        <f aca="false">IF($D93="","",IF($B93="","缺月份",IF($F93=0,"缺总工时",IF(ROUND($P93-$F93,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="94" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B94" s="28"/>
@@ -15655,6 +17121,10 @@
         <v/>
       </c>
       <c r="R94" s="27"/>
+      <c r="S94" s="21" t="str">
+        <f aca="false">IF($D94="","",IF($B94="","缺月份",IF($F94=0,"缺总工时",IF(ROUND($P94-$F94,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="95" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B95" s="28"/>
@@ -15683,6 +17153,10 @@
         <v/>
       </c>
       <c r="R95" s="27"/>
+      <c r="S95" s="21" t="str">
+        <f aca="false">IF($D95="","",IF($B95="","缺月份",IF($F95=0,"缺总工时",IF(ROUND($P95-$F95,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="96" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B96" s="28"/>
@@ -15711,6 +17185,10 @@
         <v/>
       </c>
       <c r="R96" s="27"/>
+      <c r="S96" s="21" t="str">
+        <f aca="false">IF($D96="","",IF($B96="","缺月份",IF($F96=0,"缺总工时",IF(ROUND($P96-$F96,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="97" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B97" s="28"/>
@@ -15739,6 +17217,10 @@
         <v/>
       </c>
       <c r="R97" s="27"/>
+      <c r="S97" s="21" t="str">
+        <f aca="false">IF($D97="","",IF($B97="","缺月份",IF($F97=0,"缺总工时",IF(ROUND($P97-$F97,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="98" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B98" s="28"/>
@@ -15767,6 +17249,10 @@
         <v/>
       </c>
       <c r="R98" s="27"/>
+      <c r="S98" s="21" t="str">
+        <f aca="false">IF($D98="","",IF($B98="","缺月份",IF($F98=0,"缺总工时",IF(ROUND($P98-$F98,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="99" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B99" s="28"/>
@@ -15795,6 +17281,10 @@
         <v/>
       </c>
       <c r="R99" s="27"/>
+      <c r="S99" s="21" t="str">
+        <f aca="false">IF($D99="","",IF($B99="","缺月份",IF($F99=0,"缺总工时",IF(ROUND($P99-$F99,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="100" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B100" s="28"/>
@@ -15823,6 +17313,10 @@
         <v/>
       </c>
       <c r="R100" s="27"/>
+      <c r="S100" s="21" t="str">
+        <f aca="false">IF($D100="","",IF($B100="","缺月份",IF($F100=0,"缺总工时",IF(ROUND($P100-$F100,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="101" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B101" s="28"/>
@@ -15851,6 +17345,10 @@
         <v/>
       </c>
       <c r="R101" s="27"/>
+      <c r="S101" s="21" t="str">
+        <f aca="false">IF($D101="","",IF($B101="","缺月份",IF($F101=0,"缺总工时",IF(ROUND($P101-$F101,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="102" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B102" s="28"/>
@@ -15879,10 +17377,14 @@
         <v/>
       </c>
       <c r="R102" s="27"/>
+      <c r="S102" s="21" t="str">
+        <f aca="false">IF($D102="","",IF($B102="","缺月份",IF($F102=0,"缺总工时",IF(ROUND($P102-$F102,2)&gt;0,"工时超出","√"))))</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B2:R2"/>
+  <mergeCells count="12">
+    <mergeCell ref="B2:S2"/>
     <mergeCell ref="B4:B6"/>
     <mergeCell ref="C4:C6"/>
     <mergeCell ref="D4:D6"/>
@@ -15891,6 +17393,7 @@
     <mergeCell ref="G4:G6"/>
     <mergeCell ref="H4:P4"/>
     <mergeCell ref="R4:R6"/>
+    <mergeCell ref="S4:S6"/>
     <mergeCell ref="P5:P6"/>
     <mergeCell ref="Q5:Q6"/>
   </mergeCells>
